--- a/artfynd/A 47711-2024 artfynd.xlsx
+++ b/artfynd/A 47711-2024 artfynd.xlsx
@@ -2158,7 +2158,7 @@
         <v>647146</v>
       </c>
       <c r="R14" t="n">
-        <v>6942909</v>
+        <v>6942908</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2284,7 +2284,7 @@
         <v>647146</v>
       </c>
       <c r="R15" t="n">
-        <v>6942909</v>
+        <v>6942908</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>

--- a/artfynd/A 47711-2024 artfynd.xlsx
+++ b/artfynd/A 47711-2024 artfynd.xlsx
@@ -1509,7 +1509,7 @@
         <v>136492696</v>
       </c>
       <c r="B9" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         <v>136492703</v>
       </c>
       <c r="B15" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3822,7 +3822,7 @@
         <v>136492694</v>
       </c>
       <c r="B28" t="n">
-        <v>92494</v>
+        <v>92497</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 47711-2024 artfynd.xlsx
+++ b/artfynd/A 47711-2024 artfynd.xlsx
@@ -1509,7 +1509,7 @@
         <v>136492696</v>
       </c>
       <c r="B9" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         <v>136492703</v>
       </c>
       <c r="B15" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3822,7 +3822,7 @@
         <v>136492694</v>
       </c>
       <c r="B28" t="n">
-        <v>92497</v>
+        <v>92498</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 47711-2024 artfynd.xlsx
+++ b/artfynd/A 47711-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ28"/>
+  <dimension ref="A1:AZ50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2158,7 +2158,7 @@
         <v>647146</v>
       </c>
       <c r="R14" t="n">
-        <v>6942908</v>
+        <v>6942909</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2284,7 +2284,7 @@
         <v>647146</v>
       </c>
       <c r="R15" t="n">
-        <v>6942908</v>
+        <v>6942909</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2970,10 +2970,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1322965</v>
+        <v>136727074</v>
       </c>
       <c r="B21" t="n">
-        <v>93197</v>
+        <v>79506</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2981,43 +2981,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>185</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Malarna N, Ång</t>
+          <t>Lomtjärnberget, Lomtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>647065</v>
+        <v>646493</v>
       </c>
       <c r="R21" t="n">
-        <v>6943550</v>
+        <v>6943045</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3044,12 +3040,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3060,45 +3066,31 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>Hällmarkstallskog</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr">
-        <is>
-          <t>Steget Före</t>
-        </is>
-      </c>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1322965</t>
+          <t>https://artportalen.se/Sighting/136727074</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1323582</v>
+        <v>136729186</v>
       </c>
       <c r="B22" t="n">
-        <v>93197</v>
+        <v>92377</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3106,46 +3098,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lomtjärn S, Ång</t>
+          <t>Lomtjärnen, Lomtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>646475</v>
+        <v>646697</v>
       </c>
       <c r="R22" t="n">
-        <v>6942960</v>
+        <v>6943184</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3169,12 +3152,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2011-10-24</t>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2011-10-24</t>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3185,45 +3178,31 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>Hällmarkstallskog</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr">
-        <is>
-          <t>Steget Före</t>
-        </is>
-      </c>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1323582</t>
+          <t>https://artportalen.se/Sighting/136729186</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1568573</v>
+        <v>136729010</v>
       </c>
       <c r="B23" t="n">
-        <v>91930</v>
+        <v>92106</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3231,34 +3210,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lomtjärnen S - Malarna, Ång</t>
+          <t>Lomtjärnen, Lomtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>646461</v>
+        <v>646709</v>
       </c>
       <c r="R23" t="n">
-        <v>6942878</v>
+        <v>6943225</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3285,12 +3264,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2012-11-19</t>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2012-11-19</t>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3301,50 +3290,31 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>hällmarkstallskog, nyckelbiotopsklass</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>på en grymt fin kort hällmarkstall, 200 - 300 årig</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr">
-        <is>
-          <t>Steget Före</t>
-        </is>
-      </c>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1568573</t>
+          <t>https://artportalen.se/Sighting/136729010</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1763371</v>
+        <v>136729373</v>
       </c>
       <c r="B24" t="n">
-        <v>93235</v>
+        <v>92106</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3352,43 +3322,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5966</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Malarna N, Ång</t>
+          <t>Lomtjärnen, Lomtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>647088</v>
+        <v>646714</v>
       </c>
       <c r="R24" t="n">
-        <v>6943543</v>
+        <v>6943267</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3415,12 +3376,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3431,45 +3402,31 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>Hällmarkstallskog</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr">
-        <is>
-          <t>Steget Före</t>
-        </is>
-      </c>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1763371</t>
+          <t>https://artportalen.se/Sighting/136729373</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1763372</v>
+        <v>136730129</v>
       </c>
       <c r="B25" t="n">
-        <v>93235</v>
+        <v>93396</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3477,46 +3434,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5966</v>
+        <v>4361</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Malarna N, Ång</t>
+          <t>Lomtjärnen, Lomtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>647055</v>
+        <v>646794</v>
       </c>
       <c r="R25" t="n">
-        <v>6943589</v>
+        <v>6943303</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3540,12 +3488,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3560,69 +3518,74 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr">
-        <is>
-          <t>Steget Före</t>
-        </is>
-      </c>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1763372</t>
+          <t>https://artportalen.se/Sighting/136730129</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>136492693</v>
+        <v>1322965</v>
       </c>
       <c r="B26" t="n">
-        <v>79498</v>
+        <v>93197</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6434</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Slätberget, Ång</t>
+          <t>Malarna N, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>646690</v>
+        <v>647065</v>
       </c>
       <c r="R26" t="n">
-        <v>6943229</v>
+        <v>6943550</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3646,22 +3609,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>10:27</t>
+          <t>2011-10-13</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>10:27</t>
+          <t>2011-10-13</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3672,31 +3625,45 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Hällmarkstallskog</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Hans Sundström</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr"/>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Steget Före</t>
+        </is>
+      </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136492693</t>
+          <t>https://artportalen.se/Sighting/1322965</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>136492695</v>
+        <v>1323582</v>
       </c>
       <c r="B27" t="n">
-        <v>58006</v>
+        <v>93197</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3704,51 +3671,46 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Slätberget, Ång</t>
+          <t>Lomtjärn S, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>646997</v>
+        <v>646475</v>
       </c>
       <c r="R27" t="n">
-        <v>6943476</v>
+        <v>6942960</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3772,22 +3734,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>10:46</t>
+          <t>2011-10-24</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>10:46</t>
+          <t>2011-10-24</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3798,31 +3750,45 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Hällmarkstallskog</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Hans Sundström</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Steget Före</t>
+        </is>
+      </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136492695</t>
+          <t>https://artportalen.se/Sighting/1323582</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>136492694</v>
+        <v>136729947</v>
       </c>
       <c r="B28" t="n">
-        <v>92498</v>
+        <v>93404</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3830,37 +3796,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6040186</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Slätberget, Ång</t>
+          <t>Lomtjärnen, Lomtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>646699</v>
+        <v>646748</v>
       </c>
       <c r="R28" t="n">
-        <v>6943225</v>
+        <v>6943319</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3884,22 +3850,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3908,23 +3874,2542 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136729947</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>136730396</v>
+      </c>
+      <c r="B29" t="n">
+        <v>93404</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Bergmyrorna, Bergmyrorna, Ång</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>646858</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6943381</v>
+      </c>
+      <c r="S29" t="n">
+        <v>20</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136730396</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>136729099</v>
+      </c>
+      <c r="B30" t="n">
+        <v>92499</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>4877</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis/erubescens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Lomtjärnen, Lomtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>646693</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6943233</v>
+      </c>
+      <c r="S30" t="n">
+        <v>20</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136729099</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>1568573</v>
+      </c>
+      <c r="B31" t="n">
+        <v>91930</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Lomtjärnen S - Malarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>646461</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6942878</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2012-11-19</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2012-11-19</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>hällmarkstallskog, nyckelbiotopsklass</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>på en grymt fin kort hällmarkstall, 200 - 300 årig</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Steget Före</t>
+        </is>
+      </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1568573</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>136730530</v>
+      </c>
+      <c r="B32" t="n">
+        <v>92127</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Lomtjärnen, Lomtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>646758</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6943396</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136730530</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>136727898</v>
+      </c>
+      <c r="B33" t="n">
+        <v>93430</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>5448</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Svartvit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Phellodon melaleucus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Lomtjärnberget, Lomtjärnberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>646675</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6943107</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136727898</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>136730668</v>
+      </c>
+      <c r="B34" t="n">
+        <v>93430</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>5448</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Svartvit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Phellodon melaleucus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Lomtjärnen, Lomtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>646756</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6943391</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136730668</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>1763371</v>
+      </c>
+      <c r="B35" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Malarna N, Ång</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>647088</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6943543</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2011-10-13</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2011-10-13</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Hällmarkstallskog</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>Steget Före</t>
+        </is>
+      </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1763371</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>1763372</v>
+      </c>
+      <c r="B36" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Malarna N, Ång</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>647055</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6943589</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2011-10-13</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2011-10-13</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>Steget Före</t>
+        </is>
+      </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1763372</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>136727620</v>
+      </c>
+      <c r="B37" t="n">
+        <v>93442</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Lomtjärnberget, Lomtjärnberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>646650</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6943101</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136727620</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>136728890</v>
+      </c>
+      <c r="B38" t="n">
+        <v>93442</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Lomtjärnen, Lomtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>646729</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6943226</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136728890</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>136729950</v>
+      </c>
+      <c r="B39" t="n">
+        <v>93442</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Lomtjärnen, Lomtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>646748</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6943318</v>
+      </c>
+      <c r="S39" t="n">
+        <v>20</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136729950</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>136730208</v>
+      </c>
+      <c r="B40" t="n">
+        <v>93442</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Lomtjärnen, Lomtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>646806</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6943312</v>
+      </c>
+      <c r="S40" t="n">
+        <v>20</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136730208</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>136730233</v>
+      </c>
+      <c r="B41" t="n">
+        <v>93442</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Bergmyrorna, Bergmyrorna, Ång</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>646832</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6943339</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136730233</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>136730274</v>
+      </c>
+      <c r="B42" t="n">
+        <v>93442</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Bergmyrorna, Bergmyrorna, Ång</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>646842</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6943352</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136730274</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>136730463</v>
+      </c>
+      <c r="B43" t="n">
+        <v>93442</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Bergmyrorna, Bergmyrorna, Ång</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>646862</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6943380</v>
+      </c>
+      <c r="S43" t="n">
+        <v>20</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136730463</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>136492693</v>
+      </c>
+      <c r="B44" t="n">
+        <v>79498</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Slätberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>646690</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6943229</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136492693</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>136728918</v>
+      </c>
+      <c r="B45" t="n">
+        <v>58003</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Lomtjärnen, Lomtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>646676</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6943222</v>
+      </c>
+      <c r="S45" t="n">
+        <v>20</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136728918</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>136730508</v>
+      </c>
+      <c r="B46" t="n">
+        <v>58003</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Bergmyrorna, Bergmyrorna, Ång</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>646851</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6943419</v>
+      </c>
+      <c r="S46" t="n">
+        <v>20</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136730508</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>136492695</v>
+      </c>
+      <c r="B47" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Slätberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>646997</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6943476</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136492695</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>136728716</v>
+      </c>
+      <c r="B48" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Lomtjärnen, Lomtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>646643</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6943205</v>
+      </c>
+      <c r="S48" t="n">
+        <v>20</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136728716</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>136729240</v>
+      </c>
+      <c r="B49" t="n">
+        <v>5182</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Lomtjärnen, Lomtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>646709</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6943259</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136729240</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>136492694</v>
+      </c>
+      <c r="B50" t="n">
+        <v>92498</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Slätberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>646699</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6943225</v>
+      </c>
+      <c r="S50" t="n">
+        <v>5</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136492694</t>
         </is>
@@ -3959,6 +6444,28 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 47711-2024 artfynd.xlsx
+++ b/artfynd/A 47711-2024 artfynd.xlsx
@@ -1509,7 +1509,7 @@
         <v>136492696</v>
       </c>
       <c r="B9" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>136492698</v>
       </c>
       <c r="B11" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>136492701</v>
       </c>
       <c r="B12" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>136492702</v>
       </c>
       <c r="B13" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
         <v>136492704</v>
       </c>
       <c r="B14" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2158,7 +2158,7 @@
         <v>647146</v>
       </c>
       <c r="R14" t="n">
-        <v>6942909</v>
+        <v>6942908</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2240,7 +2240,7 @@
         <v>136492703</v>
       </c>
       <c r="B15" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         <v>647146</v>
       </c>
       <c r="R15" t="n">
-        <v>6942909</v>
+        <v>6942908</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2861,7 +2861,7 @@
         <v>136492692</v>
       </c>
       <c r="B20" t="n">
-        <v>79506</v>
+        <v>79508</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
         <v>136727074</v>
       </c>
       <c r="B21" t="n">
-        <v>79506</v>
+        <v>79508</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
         <v>136729186</v>
       </c>
       <c r="B22" t="n">
-        <v>92377</v>
+        <v>92382</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3202,7 +3202,7 @@
         <v>136729010</v>
       </c>
       <c r="B23" t="n">
-        <v>92106</v>
+        <v>92111</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3314,7 +3314,7 @@
         <v>136729373</v>
       </c>
       <c r="B24" t="n">
-        <v>92106</v>
+        <v>92111</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
         <v>136730129</v>
       </c>
       <c r="B25" t="n">
-        <v>93396</v>
+        <v>93401</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3788,7 +3788,7 @@
         <v>136729947</v>
       </c>
       <c r="B28" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3900,7 +3900,7 @@
         <v>136730396</v>
       </c>
       <c r="B29" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4012,7 +4012,7 @@
         <v>136729099</v>
       </c>
       <c r="B30" t="n">
-        <v>92499</v>
+        <v>92504</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4241,7 +4241,7 @@
         <v>136730530</v>
       </c>
       <c r="B32" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
         <v>136727898</v>
       </c>
       <c r="B33" t="n">
-        <v>93430</v>
+        <v>93435</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4465,7 +4465,7 @@
         <v>136730668</v>
       </c>
       <c r="B34" t="n">
-        <v>93430</v>
+        <v>93435</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         <v>136727620</v>
       </c>
       <c r="B37" t="n">
-        <v>93442</v>
+        <v>93447</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4929,7 +4929,7 @@
         <v>136728890</v>
       </c>
       <c r="B38" t="n">
-        <v>93442</v>
+        <v>93447</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
         <v>136729950</v>
       </c>
       <c r="B39" t="n">
-        <v>93442</v>
+        <v>93447</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
         <v>136730208</v>
       </c>
       <c r="B40" t="n">
-        <v>93442</v>
+        <v>93447</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5265,7 +5265,7 @@
         <v>136730233</v>
       </c>
       <c r="B41" t="n">
-        <v>93442</v>
+        <v>93447</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5377,7 +5377,7 @@
         <v>136730274</v>
       </c>
       <c r="B42" t="n">
-        <v>93442</v>
+        <v>93447</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5489,7 +5489,7 @@
         <v>136730463</v>
       </c>
       <c r="B43" t="n">
-        <v>93442</v>
+        <v>93447</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5601,7 +5601,7 @@
         <v>136492693</v>
       </c>
       <c r="B44" t="n">
-        <v>79498</v>
+        <v>79500</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5713,7 +5713,7 @@
         <v>136728918</v>
       </c>
       <c r="B45" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5830,7 +5830,7 @@
         <v>136730508</v>
       </c>
       <c r="B46" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5947,7 +5947,7 @@
         <v>136492695</v>
       </c>
       <c r="B47" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6073,7 +6073,7 @@
         <v>136728716</v>
       </c>
       <c r="B48" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6307,7 +6307,7 @@
         <v>136492694</v>
       </c>
       <c r="B50" t="n">
-        <v>92498</v>
+        <v>92503</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 47711-2024 artfynd.xlsx
+++ b/artfynd/A 47711-2024 artfynd.xlsx
@@ -2158,7 +2158,7 @@
         <v>647146</v>
       </c>
       <c r="R14" t="n">
-        <v>6942908</v>
+        <v>6942909</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2284,7 +2284,7 @@
         <v>647146</v>
       </c>
       <c r="R15" t="n">
-        <v>6942908</v>
+        <v>6942909</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>

--- a/artfynd/A 47711-2024 artfynd.xlsx
+++ b/artfynd/A 47711-2024 artfynd.xlsx
@@ -1509,7 +1509,7 @@
         <v>136492696</v>
       </c>
       <c r="B9" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2158,7 +2158,7 @@
         <v>647146</v>
       </c>
       <c r="R14" t="n">
-        <v>6942909</v>
+        <v>6942908</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2240,7 +2240,7 @@
         <v>136492703</v>
       </c>
       <c r="B15" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         <v>647146</v>
       </c>
       <c r="R15" t="n">
-        <v>6942909</v>
+        <v>6942908</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -3090,7 +3090,7 @@
         <v>136729186</v>
       </c>
       <c r="B22" t="n">
-        <v>92382</v>
+        <v>92384</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3202,7 +3202,7 @@
         <v>136729010</v>
       </c>
       <c r="B23" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3314,7 +3314,7 @@
         <v>136729373</v>
       </c>
       <c r="B24" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
         <v>136730129</v>
       </c>
       <c r="B25" t="n">
-        <v>93401</v>
+        <v>93403</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3788,7 +3788,7 @@
         <v>136729947</v>
       </c>
       <c r="B28" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3900,7 +3900,7 @@
         <v>136730396</v>
       </c>
       <c r="B29" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4012,7 +4012,7 @@
         <v>136729099</v>
       </c>
       <c r="B30" t="n">
-        <v>92504</v>
+        <v>92506</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4241,7 +4241,7 @@
         <v>136730530</v>
       </c>
       <c r="B32" t="n">
-        <v>92132</v>
+        <v>92134</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
         <v>136727898</v>
       </c>
       <c r="B33" t="n">
-        <v>93435</v>
+        <v>93437</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4465,7 +4465,7 @@
         <v>136730668</v>
       </c>
       <c r="B34" t="n">
-        <v>93435</v>
+        <v>93437</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         <v>136727620</v>
       </c>
       <c r="B37" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4929,7 +4929,7 @@
         <v>136728890</v>
       </c>
       <c r="B38" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
         <v>136729950</v>
       </c>
       <c r="B39" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
         <v>136730208</v>
       </c>
       <c r="B40" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5265,7 +5265,7 @@
         <v>136730233</v>
       </c>
       <c r="B41" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5377,7 +5377,7 @@
         <v>136730274</v>
       </c>
       <c r="B42" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5489,7 +5489,7 @@
         <v>136730463</v>
       </c>
       <c r="B43" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6307,7 +6307,7 @@
         <v>136492694</v>
       </c>
       <c r="B50" t="n">
-        <v>92503</v>
+        <v>92505</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 47711-2024 artfynd.xlsx
+++ b/artfynd/A 47711-2024 artfynd.xlsx
@@ -1509,7 +1509,7 @@
         <v>136492696</v>
       </c>
       <c r="B9" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2158,7 +2158,7 @@
         <v>647146</v>
       </c>
       <c r="R14" t="n">
-        <v>6942909</v>
+        <v>6942908</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2240,7 +2240,7 @@
         <v>136492703</v>
       </c>
       <c r="B15" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         <v>647146</v>
       </c>
       <c r="R15" t="n">
-        <v>6942909</v>
+        <v>6942908</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2861,7 +2861,7 @@
         <v>136492692</v>
       </c>
       <c r="B20" t="n">
-        <v>79508</v>
+        <v>79512</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
         <v>136727074</v>
       </c>
       <c r="B21" t="n">
-        <v>79508</v>
+        <v>79512</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
         <v>136729186</v>
       </c>
       <c r="B22" t="n">
-        <v>92384</v>
+        <v>92386</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3202,7 +3202,7 @@
         <v>136729010</v>
       </c>
       <c r="B23" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3314,7 +3314,7 @@
         <v>136729373</v>
       </c>
       <c r="B24" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
         <v>136730129</v>
       </c>
       <c r="B25" t="n">
-        <v>93403</v>
+        <v>93405</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3788,7 +3788,7 @@
         <v>136729947</v>
       </c>
       <c r="B28" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3900,7 +3900,7 @@
         <v>136730396</v>
       </c>
       <c r="B29" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4012,7 +4012,7 @@
         <v>136729099</v>
       </c>
       <c r="B30" t="n">
-        <v>92506</v>
+        <v>92508</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4241,7 +4241,7 @@
         <v>136730530</v>
       </c>
       <c r="B32" t="n">
-        <v>92134</v>
+        <v>92136</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
         <v>136727898</v>
       </c>
       <c r="B33" t="n">
-        <v>93437</v>
+        <v>93439</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4465,7 +4465,7 @@
         <v>136730668</v>
       </c>
       <c r="B34" t="n">
-        <v>93437</v>
+        <v>93439</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         <v>136727620</v>
       </c>
       <c r="B37" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4929,7 +4929,7 @@
         <v>136728890</v>
       </c>
       <c r="B38" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
         <v>136729950</v>
       </c>
       <c r="B39" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
         <v>136730208</v>
       </c>
       <c r="B40" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5265,7 +5265,7 @@
         <v>136730233</v>
       </c>
       <c r="B41" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5377,7 +5377,7 @@
         <v>136730274</v>
       </c>
       <c r="B42" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5489,7 +5489,7 @@
         <v>136730463</v>
       </c>
       <c r="B43" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5601,7 +5601,7 @@
         <v>136492693</v>
       </c>
       <c r="B44" t="n">
-        <v>79500</v>
+        <v>79504</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6307,7 +6307,7 @@
         <v>136492694</v>
       </c>
       <c r="B50" t="n">
-        <v>92505</v>
+        <v>92507</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 47711-2024 artfynd.xlsx
+++ b/artfynd/A 47711-2024 artfynd.xlsx
@@ -1509,7 +1509,7 @@
         <v>136492696</v>
       </c>
       <c r="B9" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         <v>136492703</v>
       </c>
       <c r="B15" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2861,7 +2861,7 @@
         <v>136492692</v>
       </c>
       <c r="B20" t="n">
-        <v>79512</v>
+        <v>79514</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
         <v>136727074</v>
       </c>
       <c r="B21" t="n">
-        <v>79512</v>
+        <v>79514</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
         <v>136729186</v>
       </c>
       <c r="B22" t="n">
-        <v>92386</v>
+        <v>92388</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3202,7 +3202,7 @@
         <v>136729010</v>
       </c>
       <c r="B23" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3314,7 +3314,7 @@
         <v>136729373</v>
       </c>
       <c r="B24" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
         <v>136730129</v>
       </c>
       <c r="B25" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3788,7 +3788,7 @@
         <v>136729947</v>
       </c>
       <c r="B28" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3900,7 +3900,7 @@
         <v>136730396</v>
       </c>
       <c r="B29" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4012,7 +4012,7 @@
         <v>136729099</v>
       </c>
       <c r="B30" t="n">
-        <v>92508</v>
+        <v>92510</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4241,7 +4241,7 @@
         <v>136730530</v>
       </c>
       <c r="B32" t="n">
-        <v>92136</v>
+        <v>92138</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
         <v>136727898</v>
       </c>
       <c r="B33" t="n">
-        <v>93439</v>
+        <v>93441</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4465,7 +4465,7 @@
         <v>136730668</v>
       </c>
       <c r="B34" t="n">
-        <v>93439</v>
+        <v>93441</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         <v>136727620</v>
       </c>
       <c r="B37" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4929,7 +4929,7 @@
         <v>136728890</v>
       </c>
       <c r="B38" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
         <v>136729950</v>
       </c>
       <c r="B39" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
         <v>136730208</v>
       </c>
       <c r="B40" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5265,7 +5265,7 @@
         <v>136730233</v>
       </c>
       <c r="B41" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5377,7 +5377,7 @@
         <v>136730274</v>
       </c>
       <c r="B42" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5489,7 +5489,7 @@
         <v>136730463</v>
       </c>
       <c r="B43" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5601,7 +5601,7 @@
         <v>136492693</v>
       </c>
       <c r="B44" t="n">
-        <v>79504</v>
+        <v>79506</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6307,7 +6307,7 @@
         <v>136492694</v>
       </c>
       <c r="B50" t="n">
-        <v>92507</v>
+        <v>92509</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 47711-2024 artfynd.xlsx
+++ b/artfynd/A 47711-2024 artfynd.xlsx
@@ -1509,7 +1509,7 @@
         <v>136492696</v>
       </c>
       <c r="B9" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2158,7 +2158,7 @@
         <v>647146</v>
       </c>
       <c r="R14" t="n">
-        <v>6942908</v>
+        <v>6942909</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2240,7 +2240,7 @@
         <v>136492703</v>
       </c>
       <c r="B15" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         <v>647146</v>
       </c>
       <c r="R15" t="n">
-        <v>6942908</v>
+        <v>6942909</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2861,7 +2861,7 @@
         <v>136492692</v>
       </c>
       <c r="B20" t="n">
-        <v>79514</v>
+        <v>79515</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
         <v>136727074</v>
       </c>
       <c r="B21" t="n">
-        <v>79514</v>
+        <v>79515</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
         <v>136729186</v>
       </c>
       <c r="B22" t="n">
-        <v>92388</v>
+        <v>92389</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3202,7 +3202,7 @@
         <v>136729010</v>
       </c>
       <c r="B23" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3314,7 +3314,7 @@
         <v>136729373</v>
       </c>
       <c r="B24" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
         <v>136730129</v>
       </c>
       <c r="B25" t="n">
-        <v>93407</v>
+        <v>93408</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3788,7 +3788,7 @@
         <v>136729947</v>
       </c>
       <c r="B28" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3900,7 +3900,7 @@
         <v>136730396</v>
       </c>
       <c r="B29" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4012,7 +4012,7 @@
         <v>136729099</v>
       </c>
       <c r="B30" t="n">
-        <v>92510</v>
+        <v>92511</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4241,7 +4241,7 @@
         <v>136730530</v>
       </c>
       <c r="B32" t="n">
-        <v>92138</v>
+        <v>92139</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
         <v>136727898</v>
       </c>
       <c r="B33" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4465,7 +4465,7 @@
         <v>136730668</v>
       </c>
       <c r="B34" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         <v>136727620</v>
       </c>
       <c r="B37" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4929,7 +4929,7 @@
         <v>136728890</v>
       </c>
       <c r="B38" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
         <v>136729950</v>
       </c>
       <c r="B39" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
         <v>136730208</v>
       </c>
       <c r="B40" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5265,7 +5265,7 @@
         <v>136730233</v>
       </c>
       <c r="B41" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5377,7 +5377,7 @@
         <v>136730274</v>
       </c>
       <c r="B42" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5489,7 +5489,7 @@
         <v>136730463</v>
       </c>
       <c r="B43" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5601,7 +5601,7 @@
         <v>136492693</v>
       </c>
       <c r="B44" t="n">
-        <v>79506</v>
+        <v>79507</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6307,7 +6307,7 @@
         <v>136492694</v>
       </c>
       <c r="B50" t="n">
-        <v>92509</v>
+        <v>92510</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 47711-2024 artfynd.xlsx
+++ b/artfynd/A 47711-2024 artfynd.xlsx
@@ -1509,7 +1509,7 @@
         <v>136492696</v>
       </c>
       <c r="B9" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2158,7 +2158,7 @@
         <v>647146</v>
       </c>
       <c r="R14" t="n">
-        <v>6942909</v>
+        <v>6942908</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2240,7 +2240,7 @@
         <v>136492703</v>
       </c>
       <c r="B15" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         <v>647146</v>
       </c>
       <c r="R15" t="n">
-        <v>6942909</v>
+        <v>6942908</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -3090,7 +3090,7 @@
         <v>136729186</v>
       </c>
       <c r="B22" t="n">
-        <v>92389</v>
+        <v>92395</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3202,7 +3202,7 @@
         <v>136729010</v>
       </c>
       <c r="B23" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3314,7 +3314,7 @@
         <v>136729373</v>
       </c>
       <c r="B24" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
         <v>136730129</v>
       </c>
       <c r="B25" t="n">
-        <v>93408</v>
+        <v>93414</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3788,7 +3788,7 @@
         <v>136729947</v>
       </c>
       <c r="B28" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3900,7 +3900,7 @@
         <v>136730396</v>
       </c>
       <c r="B29" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4012,7 +4012,7 @@
         <v>136729099</v>
       </c>
       <c r="B30" t="n">
-        <v>92511</v>
+        <v>92517</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4241,7 +4241,7 @@
         <v>136730530</v>
       </c>
       <c r="B32" t="n">
-        <v>92139</v>
+        <v>92145</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
         <v>136727898</v>
       </c>
       <c r="B33" t="n">
-        <v>93442</v>
+        <v>93448</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4465,7 +4465,7 @@
         <v>136730668</v>
       </c>
       <c r="B34" t="n">
-        <v>93442</v>
+        <v>93448</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         <v>136727620</v>
       </c>
       <c r="B37" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4929,7 +4929,7 @@
         <v>136728890</v>
       </c>
       <c r="B38" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
         <v>136729950</v>
       </c>
       <c r="B39" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
         <v>136730208</v>
       </c>
       <c r="B40" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5265,7 +5265,7 @@
         <v>136730233</v>
       </c>
       <c r="B41" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5377,7 +5377,7 @@
         <v>136730274</v>
       </c>
       <c r="B42" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5489,7 +5489,7 @@
         <v>136730463</v>
       </c>
       <c r="B43" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6307,7 +6307,7 @@
         <v>136492694</v>
       </c>
       <c r="B50" t="n">
-        <v>92510</v>
+        <v>92516</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 47711-2024 artfynd.xlsx
+++ b/artfynd/A 47711-2024 artfynd.xlsx
@@ -1509,7 +1509,7 @@
         <v>136492696</v>
       </c>
       <c r="B9" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         <v>136492703</v>
       </c>
       <c r="B15" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2861,7 +2861,7 @@
         <v>136492692</v>
       </c>
       <c r="B20" t="n">
-        <v>79515</v>
+        <v>79517</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
         <v>136727074</v>
       </c>
       <c r="B21" t="n">
-        <v>79515</v>
+        <v>79517</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
         <v>136729186</v>
       </c>
       <c r="B22" t="n">
-        <v>92395</v>
+        <v>92399</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3202,7 +3202,7 @@
         <v>136729010</v>
       </c>
       <c r="B23" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3314,7 +3314,7 @@
         <v>136729373</v>
       </c>
       <c r="B24" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
         <v>136730129</v>
       </c>
       <c r="B25" t="n">
-        <v>93414</v>
+        <v>93418</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3788,7 +3788,7 @@
         <v>136729947</v>
       </c>
       <c r="B28" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3900,7 +3900,7 @@
         <v>136730396</v>
       </c>
       <c r="B29" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4012,7 +4012,7 @@
         <v>136729099</v>
       </c>
       <c r="B30" t="n">
-        <v>92517</v>
+        <v>92521</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4241,7 +4241,7 @@
         <v>136730530</v>
       </c>
       <c r="B32" t="n">
-        <v>92145</v>
+        <v>92149</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
         <v>136727898</v>
       </c>
       <c r="B33" t="n">
-        <v>93448</v>
+        <v>93452</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4465,7 +4465,7 @@
         <v>136730668</v>
       </c>
       <c r="B34" t="n">
-        <v>93448</v>
+        <v>93452</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         <v>136727620</v>
       </c>
       <c r="B37" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4929,7 +4929,7 @@
         <v>136728890</v>
       </c>
       <c r="B38" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
         <v>136729950</v>
       </c>
       <c r="B39" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
         <v>136730208</v>
       </c>
       <c r="B40" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5265,7 +5265,7 @@
         <v>136730233</v>
       </c>
       <c r="B41" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5377,7 +5377,7 @@
         <v>136730274</v>
       </c>
       <c r="B42" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5489,7 +5489,7 @@
         <v>136730463</v>
       </c>
       <c r="B43" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5601,7 +5601,7 @@
         <v>136492693</v>
       </c>
       <c r="B44" t="n">
-        <v>79507</v>
+        <v>79509</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6307,7 +6307,7 @@
         <v>136492694</v>
       </c>
       <c r="B50" t="n">
-        <v>92516</v>
+        <v>92520</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 47711-2024 artfynd.xlsx
+++ b/artfynd/A 47711-2024 artfynd.xlsx
@@ -2973,7 +2973,7 @@
         <v>136727074</v>
       </c>
       <c r="B21" t="n">
-        <v>79517</v>
+        <v>79520</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
         <v>136729186</v>
       </c>
       <c r="B22" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3202,7 +3202,7 @@
         <v>136729010</v>
       </c>
       <c r="B23" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3314,7 +3314,7 @@
         <v>136729373</v>
       </c>
       <c r="B24" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
         <v>136730129</v>
       </c>
       <c r="B25" t="n">
-        <v>93418</v>
+        <v>93420</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3788,7 +3788,7 @@
         <v>136729947</v>
       </c>
       <c r="B28" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3900,7 +3900,7 @@
         <v>136730396</v>
       </c>
       <c r="B29" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4012,7 +4012,7 @@
         <v>136729099</v>
       </c>
       <c r="B30" t="n">
-        <v>92521</v>
+        <v>92523</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4241,7 +4241,7 @@
         <v>136730530</v>
       </c>
       <c r="B32" t="n">
-        <v>92149</v>
+        <v>92151</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
         <v>136727898</v>
       </c>
       <c r="B33" t="n">
-        <v>93452</v>
+        <v>93454</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4465,7 +4465,7 @@
         <v>136730668</v>
       </c>
       <c r="B34" t="n">
-        <v>93452</v>
+        <v>93454</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         <v>136727620</v>
       </c>
       <c r="B37" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4929,7 +4929,7 @@
         <v>136728890</v>
       </c>
       <c r="B38" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
         <v>136729950</v>
       </c>
       <c r="B39" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
         <v>136730208</v>
       </c>
       <c r="B40" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5265,7 +5265,7 @@
         <v>136730233</v>
       </c>
       <c r="B41" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5377,7 +5377,7 @@
         <v>136730274</v>
       </c>
       <c r="B42" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5489,7 +5489,7 @@
         <v>136730463</v>
       </c>
       <c r="B43" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 47711-2024 artfynd.xlsx
+++ b/artfynd/A 47711-2024 artfynd.xlsx
@@ -2973,7 +2973,7 @@
         <v>136727074</v>
       </c>
       <c r="B21" t="n">
-        <v>79520</v>
+        <v>79533</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
         <v>136729186</v>
       </c>
       <c r="B22" t="n">
-        <v>92401</v>
+        <v>92414</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3202,7 +3202,7 @@
         <v>136729010</v>
       </c>
       <c r="B23" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3314,7 +3314,7 @@
         <v>136729373</v>
       </c>
       <c r="B24" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
         <v>136730129</v>
       </c>
       <c r="B25" t="n">
-        <v>93420</v>
+        <v>93433</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3788,7 +3788,7 @@
         <v>136729947</v>
       </c>
       <c r="B28" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3900,7 +3900,7 @@
         <v>136730396</v>
       </c>
       <c r="B29" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4012,7 +4012,7 @@
         <v>136729099</v>
       </c>
       <c r="B30" t="n">
-        <v>92523</v>
+        <v>92536</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4241,7 +4241,7 @@
         <v>136730530</v>
       </c>
       <c r="B32" t="n">
-        <v>92151</v>
+        <v>92164</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
         <v>136727898</v>
       </c>
       <c r="B33" t="n">
-        <v>93454</v>
+        <v>93467</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4465,7 +4465,7 @@
         <v>136730668</v>
       </c>
       <c r="B34" t="n">
-        <v>93454</v>
+        <v>93467</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         <v>136727620</v>
       </c>
       <c r="B37" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4929,7 +4929,7 @@
         <v>136728890</v>
       </c>
       <c r="B38" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
         <v>136729950</v>
       </c>
       <c r="B39" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
         <v>136730208</v>
       </c>
       <c r="B40" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5265,7 +5265,7 @@
         <v>136730233</v>
       </c>
       <c r="B41" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5377,7 +5377,7 @@
         <v>136730274</v>
       </c>
       <c r="B42" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5489,7 +5489,7 @@
         <v>136730463</v>
       </c>
       <c r="B43" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5713,7 +5713,7 @@
         <v>136728918</v>
       </c>
       <c r="B45" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5830,7 +5830,7 @@
         <v>136730508</v>
       </c>
       <c r="B46" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6073,7 +6073,7 @@
         <v>136728716</v>
       </c>
       <c r="B48" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 47711-2024 artfynd.xlsx
+++ b/artfynd/A 47711-2024 artfynd.xlsx
@@ -2973,7 +2973,7 @@
         <v>136727074</v>
       </c>
       <c r="B21" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
         <v>136729186</v>
       </c>
       <c r="B22" t="n">
-        <v>92414</v>
+        <v>92416</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3202,7 +3202,7 @@
         <v>136729010</v>
       </c>
       <c r="B23" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3314,7 +3314,7 @@
         <v>136729373</v>
       </c>
       <c r="B24" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
         <v>136730129</v>
       </c>
       <c r="B25" t="n">
-        <v>93433</v>
+        <v>93434</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3788,7 +3788,7 @@
         <v>136729947</v>
       </c>
       <c r="B28" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3900,7 +3900,7 @@
         <v>136730396</v>
       </c>
       <c r="B29" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4012,7 +4012,7 @@
         <v>136729099</v>
       </c>
       <c r="B30" t="n">
-        <v>92536</v>
+        <v>92538</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4241,7 +4241,7 @@
         <v>136730530</v>
       </c>
       <c r="B32" t="n">
-        <v>92164</v>
+        <v>92166</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
         <v>136727898</v>
       </c>
       <c r="B33" t="n">
-        <v>93467</v>
+        <v>93468</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4465,7 +4465,7 @@
         <v>136730668</v>
       </c>
       <c r="B34" t="n">
-        <v>93467</v>
+        <v>93468</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         <v>136727620</v>
       </c>
       <c r="B37" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4929,7 +4929,7 @@
         <v>136728890</v>
       </c>
       <c r="B38" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
         <v>136729950</v>
       </c>
       <c r="B39" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
         <v>136730208</v>
       </c>
       <c r="B40" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5265,7 +5265,7 @@
         <v>136730233</v>
       </c>
       <c r="B41" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5377,7 +5377,7 @@
         <v>136730274</v>
       </c>
       <c r="B42" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5489,7 +5489,7 @@
         <v>136730463</v>
       </c>
       <c r="B43" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5713,7 +5713,7 @@
         <v>136728918</v>
       </c>
       <c r="B45" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5830,7 +5830,7 @@
         <v>136730508</v>
       </c>
       <c r="B46" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6073,7 +6073,7 @@
         <v>136728716</v>
       </c>
       <c r="B48" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 47711-2024 artfynd.xlsx
+++ b/artfynd/A 47711-2024 artfynd.xlsx
@@ -2999,11 +2999,7 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Lomtjärnberget, Lomtjärnberget, Ång</t>
@@ -5739,11 +5735,7 @@
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Lomtjärnen, Lomtjärnen, Ång</t>
@@ -5856,11 +5848,7 @@
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Bergmyrorna, Bergmyrorna, Ång</t>
@@ -6099,11 +6087,7 @@
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Lomtjärnen, Lomtjärnen, Ång</t>

--- a/artfynd/A 47711-2024 artfynd.xlsx
+++ b/artfynd/A 47711-2024 artfynd.xlsx
@@ -3086,7 +3086,7 @@
         <v>136729186</v>
       </c>
       <c r="B22" t="n">
-        <v>92416</v>
+        <v>92419</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         <v>136729010</v>
       </c>
       <c r="B23" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>136729373</v>
       </c>
       <c r="B24" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3422,7 +3422,7 @@
         <v>136730129</v>
       </c>
       <c r="B25" t="n">
-        <v>93434</v>
+        <v>93437</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         <v>136729947</v>
       </c>
       <c r="B28" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         <v>136730396</v>
       </c>
       <c r="B29" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4008,7 +4008,7 @@
         <v>136729099</v>
       </c>
       <c r="B30" t="n">
-        <v>92538</v>
+        <v>92541</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4237,7 +4237,7 @@
         <v>136730530</v>
       </c>
       <c r="B32" t="n">
-        <v>92166</v>
+        <v>92169</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4349,7 +4349,7 @@
         <v>136727898</v>
       </c>
       <c r="B33" t="n">
-        <v>93468</v>
+        <v>93471</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>136730668</v>
       </c>
       <c r="B34" t="n">
-        <v>93468</v>
+        <v>93471</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4813,7 +4813,7 @@
         <v>136727620</v>
       </c>
       <c r="B37" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4925,7 +4925,7 @@
         <v>136728890</v>
       </c>
       <c r="B38" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5037,7 +5037,7 @@
         <v>136729950</v>
       </c>
       <c r="B39" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5149,7 +5149,7 @@
         <v>136730208</v>
       </c>
       <c r="B40" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         <v>136730233</v>
       </c>
       <c r="B41" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5373,7 +5373,7 @@
         <v>136730274</v>
       </c>
       <c r="B42" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5485,7 +5485,7 @@
         <v>136730463</v>
       </c>
       <c r="B43" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 47711-2024 artfynd.xlsx
+++ b/artfynd/A 47711-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ50"/>
+  <dimension ref="A1:AZ58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1322964</v>
+        <v>137306841</v>
       </c>
       <c r="B5" t="n">
-        <v>93197</v>
+        <v>93493</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,43 +1027,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Malarna N, Ång</t>
+          <t>Frölandsberget, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>647213</v>
+        <v>647990</v>
       </c>
       <c r="R5" t="n">
-        <v>6943460</v>
+        <v>6944630</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1090,12 +1081,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1106,45 +1097,31 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Hällmarkstallskog</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Steget Före</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1322964</t>
+          <t>https://artportalen.se/Sighting/137306841</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1763370</v>
+        <v>137307957</v>
       </c>
       <c r="B6" t="n">
-        <v>93235</v>
+        <v>93493</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1169,29 +1146,20 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Malarna N, Ång</t>
+          <t>Fälleberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>647213</v>
+        <v>647990</v>
       </c>
       <c r="R6" t="n">
-        <v>6943460</v>
+        <v>6944629</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1215,12 +1183,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1231,89 +1209,66 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Hällmarkstallskog</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Steget Före</t>
-        </is>
-      </c>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1763370</t>
+          <t>https://artportalen.se/Sighting/137307957</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1763374</v>
+        <v>137306302</v>
       </c>
       <c r="B7" t="n">
-        <v>93235</v>
+        <v>79580</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5966</v>
+        <v>637</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Slätberget NV, Ång</t>
+          <t>Frölandsberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>647377</v>
+        <v>648079</v>
       </c>
       <c r="R7" t="n">
-        <v>6944025</v>
+        <v>6944275</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1340,12 +1295,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Huvudsakligen 3-4 meter upp i en senvuxen gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1356,84 +1316,66 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Steget Före</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1763374</t>
+          <t>https://artportalen.se/Sighting/137306302</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1763375</v>
+        <v>137306578</v>
       </c>
       <c r="B8" t="n">
-        <v>93235</v>
+        <v>79580</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5966</v>
+        <v>637</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Slätberget, Ång</t>
+          <t>Frölandsberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>647646</v>
+        <v>648066</v>
       </c>
       <c r="R8" t="n">
-        <v>6943850</v>
+        <v>6944281</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1460,12 +1402,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1476,40 +1418,31 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Steget Före</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1763375</t>
+          <t>https://artportalen.se/Sighting/137306578</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>136492696</v>
+        <v>137303806</v>
       </c>
       <c r="B9" t="n">
-        <v>93426</v>
+        <v>93493</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1517,37 +1450,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Slätberget, Ång</t>
+          <t>Frölandsberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>647044</v>
+        <v>648115</v>
       </c>
       <c r="R9" t="n">
-        <v>6943285</v>
+        <v>6944399</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1571,22 +1504,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>10:53</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>10:53</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1601,27 +1524,27 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136492696</t>
+          <t>https://artportalen.se/Sighting/137303806</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1763367</v>
+        <v>137304584</v>
       </c>
       <c r="B10" t="n">
-        <v>93235</v>
+        <v>93493</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,26 +1569,17 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Malarna, Ång</t>
+          <t>Frölandsberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>647086</v>
+        <v>648168</v>
       </c>
       <c r="R10" t="n">
-        <v>6943195</v>
+        <v>6944274</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1692,12 +1606,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1708,45 +1622,31 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Hällmarkstallskog</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>Steget Före</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1763367</t>
+          <t>https://artportalen.se/Sighting/137304584</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>136492698</v>
+        <v>1322964</v>
       </c>
       <c r="B11" t="n">
-        <v>58008</v>
+        <v>93197</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1754,45 +1654,46 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Slätberget, Ång</t>
+          <t>Malarna N, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>647146</v>
+        <v>647213</v>
       </c>
       <c r="R11" t="n">
-        <v>6942982</v>
+        <v>6943460</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1816,27 +1717,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>11:11</t>
+          <t>2011-10-13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall. På bilden syns det äldre ringhacket, men det färska som sitter strax ovanför syns desto sämre. Med kikare i fält syns det färska ringhacket betydligt bättre.</t>
+          <t>2011-10-13</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1847,74 +1733,83 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Hällmarkstallskog</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Hans Sundström</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Steget Före</t>
+        </is>
+      </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136492698</t>
+          <t>https://artportalen.se/Sighting/1322964</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>136492701</v>
+        <v>137303303</v>
       </c>
       <c r="B12" t="n">
-        <v>58008</v>
+        <v>92121</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Slätberget, Ång</t>
+          <t>Frölandsberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>647146</v>
+        <v>647859</v>
       </c>
       <c r="R12" t="n">
-        <v>6942952</v>
+        <v>6944480</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1938,27 +1833,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:15</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Färska och årsfärska ringhack på tall</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1973,27 +1863,27 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136492701</t>
+          <t>https://artportalen.se/Sighting/137303303</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>136492702</v>
+        <v>1763370</v>
       </c>
       <c r="B13" t="n">
-        <v>58008</v>
+        <v>93235</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2001,42 +1891,46 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>5966</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Slätberget, Ång</t>
+          <t>Malarna N, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>647143</v>
+        <v>647213</v>
       </c>
       <c r="R13" t="n">
-        <v>6942924</v>
+        <v>6943460</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2060,27 +1954,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>11:18</t>
+          <t>2011-10-13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>11:18</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>2011-10-13</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2091,31 +1970,45 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Hällmarkstallskog</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Hans Sundström</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Steget Före</t>
+        </is>
+      </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136492702</t>
+          <t>https://artportalen.se/Sighting/1763370</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>136492704</v>
+        <v>1763374</v>
       </c>
       <c r="B14" t="n">
-        <v>58008</v>
+        <v>93235</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2123,45 +2016,46 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>5966</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Slätberget, Ång</t>
+          <t>Slätberget NV, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>647146</v>
+        <v>647377</v>
       </c>
       <c r="R14" t="n">
-        <v>6942908</v>
+        <v>6944025</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2185,27 +2079,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>11:25</t>
+          <t>2011-10-13</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>11:25</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ca 2 meter ovan mark i asp. Hade inget måttband med mig varför bohålsdiametern inte kunde mätas. Hålet såg dock relativt litet ut varför jag bedömer det som sannolikt uthackat av tretåig hackspett.</t>
+          <t>2011-10-13</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2216,63 +2095,72 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Hans Sundström</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Steget Före</t>
+        </is>
+      </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136492704</t>
+          <t>https://artportalen.se/Sighting/1763374</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>136492703</v>
+        <v>1763375</v>
       </c>
       <c r="B15" t="n">
-        <v>99372</v>
+        <v>93235</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2281,13 +2169,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>647146</v>
+        <v>647646</v>
       </c>
       <c r="R15" t="n">
-        <v>6942908</v>
+        <v>6943850</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2311,22 +2199,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>11:21</t>
+          <t>2011-10-13</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>11:21</t>
+          <t>2011-10-13</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2337,78 +2215,81 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Hans Sundström</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Steget Före</t>
+        </is>
+      </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136492703</t>
+          <t>https://artportalen.se/Sighting/1763375</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1322962</v>
+        <v>137307954</v>
       </c>
       <c r="B16" t="n">
-        <v>93197</v>
+        <v>79537</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>6434</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Malarna N, Ång</t>
+          <t>Fälleberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>647245</v>
+        <v>647884</v>
       </c>
       <c r="R16" t="n">
-        <v>6943405</v>
+        <v>6944388</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2432,12 +2313,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2446,47 +2337,49 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>Hällmarkstallskog</t>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>Steget Före</t>
-        </is>
-      </c>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1322962</t>
+          <t>https://artportalen.se/Sighting/137307954</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1322963</v>
+        <v>136492696</v>
       </c>
       <c r="B17" t="n">
-        <v>93197</v>
+        <v>93426</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2511,29 +2404,20 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Malarna N, Ång</t>
+          <t>Slätberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>647228</v>
+        <v>647044</v>
       </c>
       <c r="R17" t="n">
-        <v>6943441</v>
+        <v>6943285</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2557,12 +2441,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2573,42 +2467,28 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>Hällmarkstallskog</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>Steget Före</t>
-        </is>
-      </c>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1322963</t>
+          <t>https://artportalen.se/Sighting/136492696</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1763368</v>
+        <v>1763367</v>
       </c>
       <c r="B18" t="n">
         <v>93235</v>
@@ -2638,7 +2518,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2648,14 +2528,14 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Malarna N, Ång</t>
+          <t>Malarna, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>647245</v>
+        <v>647086</v>
       </c>
       <c r="R18" t="n">
-        <v>6943405</v>
+        <v>6943195</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2727,16 +2607,16 @@
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1763368</t>
+          <t>https://artportalen.se/Sighting/1763367</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1763369</v>
+        <v>136492698</v>
       </c>
       <c r="B19" t="n">
-        <v>93235</v>
+        <v>58008</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2744,46 +2624,45 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5966</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Malarna N, Ång</t>
+          <t>Slätberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>647228</v>
+        <v>647146</v>
       </c>
       <c r="R19" t="n">
-        <v>6943441</v>
+        <v>6942982</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2807,12 +2686,27 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall. På bilden syns det äldre ringhacket, men det färska som sitter strax ovanför syns desto sämre. Med kikare i fält syns det färska ringhacket betydligt bättre.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2823,45 +2717,31 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>Hällmarkstallskog</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr">
-        <is>
-          <t>Steget Före</t>
-        </is>
-      </c>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1763369</t>
+          <t>https://artportalen.se/Sighting/136492698</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>136492692</v>
+        <v>136492701</v>
       </c>
       <c r="B20" t="n">
-        <v>79517</v>
+        <v>58008</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2869,34 +2749,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Slätberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>646499</v>
+        <v>647146</v>
       </c>
       <c r="R20" t="n">
-        <v>6943041</v>
+        <v>6942952</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2928,7 +2813,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2938,7 +2823,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Färska och årsfärska ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2964,16 +2854,16 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136492692</t>
+          <t>https://artportalen.se/Sighting/136492701</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>136727074</v>
+        <v>136492702</v>
       </c>
       <c r="B21" t="n">
-        <v>79535</v>
+        <v>58008</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2981,38 +2871,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lomtjärnberget, Lomtjärnberget, Ång</t>
+          <t>Slätberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>646493</v>
+        <v>647143</v>
       </c>
       <c r="R21" t="n">
-        <v>6943045</v>
+        <v>6942924</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3036,22 +2930,27 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3066,27 +2965,27 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136727074</t>
+          <t>https://artportalen.se/Sighting/136492702</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>136729186</v>
+        <v>136492704</v>
       </c>
       <c r="B22" t="n">
-        <v>92419</v>
+        <v>58008</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3094,37 +2993,45 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lomtjärnen, Lomtjärnen, Ång</t>
+          <t>Slätberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>646697</v>
+        <v>647146</v>
       </c>
       <c r="R22" t="n">
-        <v>6943184</v>
+        <v>6942908</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3148,22 +3055,27 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ca 2 meter ovan mark i asp. Hade inget måttband med mig varför bohålsdiametern inte kunde mätas. Hålet såg dock relativt litet ut varför jag bedömer det som sannolikt uthackat av tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3178,65 +3090,74 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136729186</t>
+          <t>https://artportalen.se/Sighting/136492704</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>136729010</v>
+        <v>136492703</v>
       </c>
       <c r="B23" t="n">
-        <v>92148</v>
+        <v>99372</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lomtjärnen, Lomtjärnen, Ång</t>
+          <t>Slätberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>646709</v>
+        <v>647146</v>
       </c>
       <c r="R23" t="n">
-        <v>6943225</v>
+        <v>6942908</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3260,22 +3181,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3290,27 +3211,27 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136729010</t>
+          <t>https://artportalen.se/Sighting/136492703</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>136729373</v>
+        <v>1322962</v>
       </c>
       <c r="B24" t="n">
-        <v>92148</v>
+        <v>93197</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3318,34 +3239,43 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lomtjärnen, Lomtjärnen, Ång</t>
+          <t>Malarna N, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>646714</v>
+        <v>647245</v>
       </c>
       <c r="R24" t="n">
-        <v>6943267</v>
+        <v>6943405</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3372,22 +3302,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>14:21</t>
+          <t>2011-10-13</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>14:21</t>
+          <t>2011-10-13</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3398,31 +3318,45 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Hällmarkstallskog</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Hans Sundström</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Steget Före</t>
+        </is>
+      </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136729373</t>
+          <t>https://artportalen.se/Sighting/1322962</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>136730129</v>
+        <v>1322963</v>
       </c>
       <c r="B25" t="n">
-        <v>93437</v>
+        <v>93197</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3430,37 +3364,46 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Lomtjärnen, Lomtjärnen, Ång</t>
+          <t>Malarna N, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>646794</v>
+        <v>647228</v>
       </c>
       <c r="R25" t="n">
-        <v>6943303</v>
+        <v>6943441</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3484,22 +3427,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>14:49</t>
+          <t>2011-10-13</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>14:49</t>
+          <t>2011-10-13</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3510,31 +3443,45 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Hällmarkstallskog</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Hans Sundström</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Steget Före</t>
+        </is>
+      </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136730129</t>
+          <t>https://artportalen.se/Sighting/1322963</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1322965</v>
+        <v>1763368</v>
       </c>
       <c r="B26" t="n">
-        <v>93197</v>
+        <v>93235</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3542,26 +3489,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3575,10 +3522,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>647065</v>
+        <v>647245</v>
       </c>
       <c r="R26" t="n">
-        <v>6943550</v>
+        <v>6943405</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3650,16 +3597,16 @@
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1322965</t>
+          <t>https://artportalen.se/Sighting/1763368</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1323582</v>
+        <v>1763369</v>
       </c>
       <c r="B27" t="n">
-        <v>93197</v>
+        <v>93235</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3667,26 +3614,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3696,14 +3643,14 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Lomtjärn S, Ång</t>
+          <t>Malarna N, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>646475</v>
+        <v>647228</v>
       </c>
       <c r="R27" t="n">
-        <v>6942960</v>
+        <v>6943441</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3730,12 +3677,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2011-10-24</t>
+          <t>2011-10-13</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2011-10-24</t>
+          <t>2011-10-13</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3775,16 +3722,16 @@
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1323582</t>
+          <t>https://artportalen.se/Sighting/1763369</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>136729947</v>
+        <v>136492692</v>
       </c>
       <c r="B28" t="n">
-        <v>93445</v>
+        <v>79517</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3792,37 +3739,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>185</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lomtjärnen, Lomtjärnen, Ång</t>
+          <t>Slätberget, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>646748</v>
+        <v>646499</v>
       </c>
       <c r="R28" t="n">
-        <v>6943319</v>
+        <v>6943041</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3846,22 +3793,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3876,27 +3823,27 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136729947</t>
+          <t>https://artportalen.se/Sighting/136492692</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>136730396</v>
+        <v>136727074</v>
       </c>
       <c r="B29" t="n">
-        <v>93445</v>
+        <v>79545</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3904,37 +3851,38 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>185</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Bergmyrorna, Bergmyrorna, Ång</t>
+          <t>Lomtjärnberget, Lomtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>646858</v>
+        <v>646493</v>
       </c>
       <c r="R29" t="n">
-        <v>6943381</v>
+        <v>6943045</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3963,7 +3911,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3973,7 +3921,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3999,36 +3947,40 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136730396</t>
+          <t>https://artportalen.se/Sighting/136727074</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>136729099</v>
+        <v>136729186</v>
       </c>
       <c r="B30" t="n">
-        <v>92541</v>
+        <v>92429</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4877</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Leptoporus mollis/erubescens</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4036,10 +3988,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>646693</v>
+        <v>646697</v>
       </c>
       <c r="R30" t="n">
-        <v>6943233</v>
+        <v>6943184</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -4071,7 +4023,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4081,7 +4033,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4107,16 +4059,16 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136729099</t>
+          <t>https://artportalen.se/Sighting/136729186</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>1568573</v>
+        <v>136729010</v>
       </c>
       <c r="B31" t="n">
-        <v>91930</v>
+        <v>92158</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4124,34 +4076,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lomtjärnen S - Malarna, Ång</t>
+          <t>Lomtjärnen, Lomtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>646461</v>
+        <v>646709</v>
       </c>
       <c r="R31" t="n">
-        <v>6942878</v>
+        <v>6943225</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4178,12 +4130,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2012-11-19</t>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2012-11-19</t>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4194,50 +4156,31 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>hällmarkstallskog, nyckelbiotopsklass</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>på en grymt fin kort hällmarkstall, 200 - 300 årig</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr">
-        <is>
-          <t>Steget Före</t>
-        </is>
-      </c>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1568573</t>
+          <t>https://artportalen.se/Sighting/136729010</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>136730530</v>
+        <v>136729373</v>
       </c>
       <c r="B32" t="n">
-        <v>92169</v>
+        <v>92158</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4245,21 +4188,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4269,10 +4212,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>646758</v>
+        <v>646714</v>
       </c>
       <c r="R32" t="n">
-        <v>6943396</v>
+        <v>6943267</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4304,7 +4247,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4314,7 +4257,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4340,16 +4283,16 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136730530</t>
+          <t>https://artportalen.se/Sighting/136729373</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>136727898</v>
+        <v>136730129</v>
       </c>
       <c r="B33" t="n">
-        <v>93471</v>
+        <v>93447</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4357,37 +4300,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5448</v>
+        <v>4361</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lomtjärnberget, Lomtjärnberget, Ång</t>
+          <t>Lomtjärnen, Lomtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>646675</v>
+        <v>646794</v>
       </c>
       <c r="R33" t="n">
-        <v>6943107</v>
+        <v>6943303</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4416,7 +4359,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4426,7 +4369,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4441,27 +4384,27 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136727898</t>
+          <t>https://artportalen.se/Sighting/136730129</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>136730668</v>
+        <v>1322965</v>
       </c>
       <c r="B34" t="n">
-        <v>93471</v>
+        <v>93197</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4469,34 +4412,43 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5448</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Lomtjärnen, Lomtjärnen, Ång</t>
+          <t>Malarna N, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>646756</v>
+        <v>647065</v>
       </c>
       <c r="R34" t="n">
-        <v>6943391</v>
+        <v>6943550</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4523,22 +4475,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>15:19</t>
+          <t>2011-10-13</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>15:19</t>
+          <t>2011-10-13</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4549,31 +4491,45 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>Hällmarkstallskog</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Hans Sundström</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr"/>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>Steget Före</t>
+        </is>
+      </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136730668</t>
+          <t>https://artportalen.se/Sighting/1322965</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>1763371</v>
+        <v>1323582</v>
       </c>
       <c r="B35" t="n">
-        <v>93235</v>
+        <v>93197</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4581,26 +4537,26 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4610,14 +4566,14 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Malarna N, Ång</t>
+          <t>Lomtjärn S, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>647088</v>
+        <v>646475</v>
       </c>
       <c r="R35" t="n">
-        <v>6943543</v>
+        <v>6942960</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4644,12 +4600,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2011-10-24</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2011-10-24</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4689,16 +4645,16 @@
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1763371</t>
+          <t>https://artportalen.se/Sighting/1323582</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>1763372</v>
+        <v>136729947</v>
       </c>
       <c r="B36" t="n">
-        <v>93235</v>
+        <v>93455</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4706,43 +4662,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Malarna N, Ång</t>
+          <t>Lomtjärnen, Lomtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>647055</v>
+        <v>646748</v>
       </c>
       <c r="R36" t="n">
-        <v>6943589</v>
+        <v>6943319</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4769,12 +4716,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4789,31 +4746,27 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr">
-        <is>
-          <t>Steget Före</t>
-        </is>
-      </c>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1763372</t>
+          <t>https://artportalen.se/Sighting/136729947</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>136727620</v>
+        <v>136730396</v>
       </c>
       <c r="B37" t="n">
-        <v>93483</v>
+        <v>93455</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4821,37 +4774,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Lomtjärnberget, Lomtjärnberget, Ång</t>
+          <t>Bergmyrorna, Bergmyrorna, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>646650</v>
+        <v>646858</v>
       </c>
       <c r="R37" t="n">
-        <v>6943101</v>
+        <v>6943381</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4880,7 +4833,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4890,7 +4843,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4905,51 +4858,47 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136727620</t>
+          <t>https://artportalen.se/Sighting/136730396</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>136728890</v>
+        <v>136729099</v>
       </c>
       <c r="B38" t="n">
-        <v>93483</v>
+        <v>92551</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5966</v>
+        <v>4877</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Leptoporus mollis/erubescens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4957,13 +4906,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>646729</v>
+        <v>646693</v>
       </c>
       <c r="R38" t="n">
-        <v>6943226</v>
+        <v>6943233</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4992,7 +4941,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5002,7 +4951,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5017,27 +4966,27 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136728890</t>
+          <t>https://artportalen.se/Sighting/136729099</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>136729950</v>
+        <v>1568573</v>
       </c>
       <c r="B39" t="n">
-        <v>93483</v>
+        <v>91930</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5045,37 +4994,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Lomtjärnen, Lomtjärnen, Ång</t>
+          <t>Lomtjärnen S - Malarna, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>646748</v>
+        <v>646461</v>
       </c>
       <c r="R39" t="n">
-        <v>6943318</v>
+        <v>6942878</v>
       </c>
       <c r="S39" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5099,22 +5048,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>14:43</t>
+          <t>2012-11-19</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>14:43</t>
+          <t>2012-11-19</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5125,31 +5064,50 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>hällmarkstallskog, nyckelbiotopsklass</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>på en grymt fin kort hällmarkstall, 200 - 300 årig</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Hans Sundström</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr"/>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>Steget Före</t>
+        </is>
+      </c>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136729950</t>
+          <t>https://artportalen.se/Sighting/1568573</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>136730208</v>
+        <v>136730530</v>
       </c>
       <c r="B40" t="n">
-        <v>93483</v>
+        <v>92179</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5157,21 +5115,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5181,13 +5139,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>646806</v>
+        <v>646758</v>
       </c>
       <c r="R40" t="n">
-        <v>6943312</v>
+        <v>6943396</v>
       </c>
       <c r="S40" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5216,7 +5174,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5226,7 +5184,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5241,27 +5199,27 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136730208</t>
+          <t>https://artportalen.se/Sighting/136730530</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>136730233</v>
+        <v>136727898</v>
       </c>
       <c r="B41" t="n">
-        <v>93483</v>
+        <v>93481</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5269,34 +5227,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5966</v>
+        <v>5448</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Bergmyrorna, Bergmyrorna, Ång</t>
+          <t>Lomtjärnberget, Lomtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>646832</v>
+        <v>646675</v>
       </c>
       <c r="R41" t="n">
-        <v>6943339</v>
+        <v>6943107</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5328,7 +5286,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5338,7 +5296,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5364,16 +5322,16 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136730233</t>
+          <t>https://artportalen.se/Sighting/136727898</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>136730274</v>
+        <v>136730668</v>
       </c>
       <c r="B42" t="n">
-        <v>93483</v>
+        <v>93481</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5381,34 +5339,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5966</v>
+        <v>5448</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Bergmyrorna, Bergmyrorna, Ång</t>
+          <t>Lomtjärnen, Lomtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>646842</v>
+        <v>646756</v>
       </c>
       <c r="R42" t="n">
-        <v>6943352</v>
+        <v>6943391</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5440,7 +5398,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5450,7 +5408,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5476,16 +5434,16 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136730274</t>
+          <t>https://artportalen.se/Sighting/136730668</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>136730463</v>
+        <v>1763371</v>
       </c>
       <c r="B43" t="n">
-        <v>93483</v>
+        <v>93235</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5510,20 +5468,29 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Bergmyrorna, Bergmyrorna, Ång</t>
+          <t>Malarna N, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>646862</v>
+        <v>647088</v>
       </c>
       <c r="R43" t="n">
-        <v>6943380</v>
+        <v>6943543</v>
       </c>
       <c r="S43" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5547,22 +5514,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>15:04</t>
+          <t>2011-10-13</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>15:04</t>
+          <t>2011-10-13</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5573,69 +5530,92 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>Hällmarkstallskog</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Hans Sundström</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
-        </is>
-      </c>
-      <c r="AY43" t="inlineStr"/>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>Steget Före</t>
+        </is>
+      </c>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136730463</t>
+          <t>https://artportalen.se/Sighting/1763371</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>136492693</v>
+        <v>1763372</v>
       </c>
       <c r="B44" t="n">
-        <v>79509</v>
+        <v>93235</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6434</v>
+        <v>5966</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Slätberget, Ång</t>
+          <t>Malarna N, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>646690</v>
+        <v>647055</v>
       </c>
       <c r="R44" t="n">
-        <v>6943229</v>
+        <v>6943589</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5659,22 +5639,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>10:27</t>
+          <t>2011-10-13</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>10:27</t>
+          <t>2011-10-13</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5689,66 +5659,69 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Hans Sundström</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr"/>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>Steget Före</t>
+        </is>
+      </c>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136492693</t>
+          <t>https://artportalen.se/Sighting/1763372</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>136728918</v>
+        <v>136727620</v>
       </c>
       <c r="B45" t="n">
-        <v>58020</v>
+        <v>93493</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Lomtjärnen, Lomtjärnen, Ång</t>
+          <t>Lomtjärnberget, Lomtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>646676</v>
+        <v>646650</v>
       </c>
       <c r="R45" t="n">
-        <v>6943222</v>
+        <v>6943101</v>
       </c>
       <c r="S45" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5777,7 +5750,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5787,7 +5760,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5802,66 +5775,65 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136728918</t>
+          <t>https://artportalen.se/Sighting/136727620</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>136730508</v>
+        <v>136728890</v>
       </c>
       <c r="B46" t="n">
-        <v>58020</v>
+        <v>93493</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Bergmyrorna, Bergmyrorna, Ång</t>
+          <t>Lomtjärnen, Lomtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>646851</v>
+        <v>646729</v>
       </c>
       <c r="R46" t="n">
-        <v>6943419</v>
+        <v>6943226</v>
       </c>
       <c r="S46" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5890,7 +5862,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5900,7 +5872,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5915,27 +5887,27 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136730508</t>
+          <t>https://artportalen.se/Sighting/136728890</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>136492695</v>
+        <v>136729950</v>
       </c>
       <c r="B47" t="n">
-        <v>58008</v>
+        <v>93493</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5943,51 +5915,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>5966</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Slätberget, Ång</t>
+          <t>Lomtjärnen, Lomtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>646997</v>
+        <v>646748</v>
       </c>
       <c r="R47" t="n">
-        <v>6943476</v>
+        <v>6943318</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6011,22 +5969,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6041,27 +5999,27 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136492695</t>
+          <t>https://artportalen.se/Sighting/136729950</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>136728716</v>
+        <v>136730208</v>
       </c>
       <c r="B48" t="n">
-        <v>58023</v>
+        <v>93493</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6069,35 +6027,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>5966</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Lomtjärnen, Lomtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>646643</v>
+        <v>646806</v>
       </c>
       <c r="R48" t="n">
-        <v>6943205</v>
+        <v>6943312</v>
       </c>
       <c r="S48" t="n">
         <v>20</v>
@@ -6129,7 +6086,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6139,12 +6096,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:46</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6170,51 +6122,51 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136728716</t>
+          <t>https://artportalen.se/Sighting/136730208</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>136729240</v>
+        <v>136730233</v>
       </c>
       <c r="B49" t="n">
-        <v>5182</v>
+        <v>93493</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100526</v>
+        <v>5966</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Lomtjärnen, Lomtjärnen, Ång</t>
+          <t>Bergmyrorna, Bergmyrorna, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>646709</v>
+        <v>646832</v>
       </c>
       <c r="R49" t="n">
-        <v>6943259</v>
+        <v>6943339</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6246,7 +6198,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6256,7 +6208,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6282,16 +6234,16 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136729240</t>
+          <t>https://artportalen.se/Sighting/136730233</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>136492694</v>
+        <v>136730274</v>
       </c>
       <c r="B50" t="n">
-        <v>92520</v>
+        <v>93493</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6299,37 +6251,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6040186</v>
+        <v>5966</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Slätberget, Ång</t>
+          <t>Bergmyrorna, Bergmyrorna, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>646699</v>
+        <v>646842</v>
       </c>
       <c r="R50" t="n">
-        <v>6943225</v>
+        <v>6943352</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6353,22 +6305,22 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6377,23 +6329,941 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136730274</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>136730463</v>
+      </c>
+      <c r="B51" t="n">
+        <v>93493</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Bergmyrorna, Bergmyrorna, Ång</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>646862</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6943380</v>
+      </c>
+      <c r="S51" t="n">
+        <v>20</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136730463</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>136492693</v>
+      </c>
+      <c r="B52" t="n">
+        <v>79509</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Slätberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>646690</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6943229</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136492693</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>136728918</v>
+      </c>
+      <c r="B53" t="n">
+        <v>58030</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Lomtjärnen, Lomtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>646676</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6943222</v>
+      </c>
+      <c r="S53" t="n">
+        <v>20</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136728918</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>136730508</v>
+      </c>
+      <c r="B54" t="n">
+        <v>58030</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Bergmyrorna, Bergmyrorna, Ång</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>646851</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6943419</v>
+      </c>
+      <c r="S54" t="n">
+        <v>20</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136730508</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>136492695</v>
+      </c>
+      <c r="B55" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Slätberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>646997</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6943476</v>
+      </c>
+      <c r="S55" t="n">
+        <v>5</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136492695</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>136728716</v>
+      </c>
+      <c r="B56" t="n">
+        <v>58033</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Lomtjärnen, Lomtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>646643</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6943205</v>
+      </c>
+      <c r="S56" t="n">
+        <v>20</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136728716</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>136729240</v>
+      </c>
+      <c r="B57" t="n">
+        <v>5188</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Lomtjärnen, Lomtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>646709</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6943259</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136729240</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>136492694</v>
+      </c>
+      <c r="B58" t="n">
+        <v>92520</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Slätberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>646699</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6943225</v>
+      </c>
+      <c r="S58" t="n">
+        <v>5</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136492694</t>
         </is>
@@ -6450,6 +7320,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 47711-2024 artfynd.xlsx
+++ b/artfynd/A 47711-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ58"/>
+  <dimension ref="A1:AZ66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1019,7 +1019,7 @@
         <v>137306841</v>
       </c>
       <c r="B5" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>137307957</v>
       </c>
       <c r="B6" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1439,32 +1439,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>137303806</v>
+        <v>137325198</v>
       </c>
       <c r="B9" t="n">
-        <v>93493</v>
+        <v>79580</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5966</v>
+        <v>637</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1474,10 +1474,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>648115</v>
+        <v>648033</v>
       </c>
       <c r="R9" t="n">
-        <v>6944399</v>
+        <v>6944317</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1504,12 +1504,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1535,16 +1540,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137303806</t>
+          <t>https://artportalen.se/Sighting/137325198</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>137304584</v>
+        <v>137326956</v>
       </c>
       <c r="B10" t="n">
-        <v>93493</v>
+        <v>93456</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1552,21 +1557,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1576,10 +1581,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>648168</v>
+        <v>648123</v>
       </c>
       <c r="R10" t="n">
-        <v>6944274</v>
+        <v>6944279</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1606,12 +1611,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1637,16 +1642,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137304584</t>
+          <t>https://artportalen.se/Sighting/137326956</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1322964</v>
+        <v>137303806</v>
       </c>
       <c r="B11" t="n">
-        <v>93197</v>
+        <v>93494</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1654,43 +1659,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Malarna N, Ång</t>
+          <t>Frölandsberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>647213</v>
+        <v>648115</v>
       </c>
       <c r="R11" t="n">
-        <v>6943460</v>
+        <v>6944399</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1717,12 +1713,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1733,67 +1729,53 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Hällmarkstallskog</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>Steget Före</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1322964</t>
+          <t>https://artportalen.se/Sighting/137303806</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>137303303</v>
+        <v>137304584</v>
       </c>
       <c r="B12" t="n">
-        <v>92121</v>
+        <v>93494</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>5966</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1803,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>647859</v>
+        <v>648168</v>
       </c>
       <c r="R12" t="n">
-        <v>6944480</v>
+        <v>6944274</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1836,19 +1818,9 @@
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>14:20</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>14:20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1863,71 +1835,62 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137303303</t>
+          <t>https://artportalen.se/Sighting/137304584</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1763370</v>
+        <v>137326463</v>
       </c>
       <c r="B13" t="n">
-        <v>93235</v>
+        <v>79513</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Malarna N, Ång</t>
+          <t>Frölandsberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>647213</v>
+        <v>647966</v>
       </c>
       <c r="R13" t="n">
-        <v>6943460</v>
+        <v>6944439</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1954,12 +1917,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1970,45 +1933,31 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Hällmarkstallskog</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>Steget Före</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1763370</t>
+          <t>https://artportalen.se/Sighting/137326463</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1763374</v>
+        <v>1322964</v>
       </c>
       <c r="B14" t="n">
-        <v>93235</v>
+        <v>93197</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2016,26 +1965,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2045,14 +1994,14 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Slätberget NV, Ång</t>
+          <t>Malarna N, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>647377</v>
+        <v>647213</v>
       </c>
       <c r="R14" t="n">
-        <v>6944025</v>
+        <v>6943460</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2096,9 +2045,14 @@
       <c r="AG14" t="b">
         <v>0</v>
       </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Hällmarkstallskog</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2119,60 +2073,51 @@
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1763374</t>
+          <t>https://artportalen.se/Sighting/1322964</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1763375</v>
+        <v>137303303</v>
       </c>
       <c r="B15" t="n">
-        <v>93235</v>
+        <v>92122</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5966</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Slätberget, Ång</t>
+          <t>Frölandsberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>647646</v>
+        <v>647859</v>
       </c>
       <c r="R15" t="n">
-        <v>6943850</v>
+        <v>6944480</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2199,12 +2144,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2215,81 +2170,78 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>Steget Före</t>
-        </is>
-      </c>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1763375</t>
+          <t>https://artportalen.se/Sighting/137303303</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>137307954</v>
+        <v>1763370</v>
       </c>
       <c r="B16" t="n">
-        <v>79537</v>
+        <v>93235</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6434</v>
+        <v>5966</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Fälleberget, Ång</t>
+          <t>Malarna N, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>647884</v>
+        <v>647213</v>
       </c>
       <c r="R16" t="n">
-        <v>6944388</v>
+        <v>6943460</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2313,22 +2265,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>13:59</t>
+          <t>2011-10-13</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>13:59</t>
+          <t>2011-10-13</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2337,49 +2279,47 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Hällmarkstallskog</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Hans Sundström</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Steget Före</t>
+        </is>
+      </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137307954</t>
+          <t>https://artportalen.se/Sighting/1763370</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>136492696</v>
+        <v>1763374</v>
       </c>
       <c r="B17" t="n">
-        <v>93426</v>
+        <v>93235</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2387,37 +2327,46 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Slätberget, Ång</t>
+          <t>Slätberget NV, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>647044</v>
+        <v>647377</v>
       </c>
       <c r="R17" t="n">
-        <v>6943285</v>
+        <v>6944025</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2441,22 +2390,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>10:53</t>
+          <t>2011-10-13</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>10:53</t>
+          <t>2011-10-13</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2467,28 +2406,37 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Hans Sundström</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Steget Före</t>
+        </is>
+      </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136492696</t>
+          <t>https://artportalen.se/Sighting/1763374</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1763367</v>
+        <v>1763375</v>
       </c>
       <c r="B18" t="n">
         <v>93235</v>
@@ -2518,7 +2466,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2528,14 +2476,14 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Malarna, Ång</t>
+          <t>Slätberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>647086</v>
+        <v>647646</v>
       </c>
       <c r="R18" t="n">
-        <v>6943195</v>
+        <v>6943850</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2579,14 +2527,9 @@
       <c r="AG18" t="b">
         <v>0</v>
       </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Hällmarkstallskog</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2607,16 +2550,16 @@
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1763367</t>
+          <t>https://artportalen.se/Sighting/1763375</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>136492698</v>
+        <v>137323297</v>
       </c>
       <c r="B19" t="n">
-        <v>58008</v>
+        <v>93494</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2624,45 +2567,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>5966</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Slätberget, Ång</t>
+          <t>Frölandsberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>647146</v>
+        <v>647851</v>
       </c>
       <c r="R19" t="n">
-        <v>6942982</v>
+        <v>6944063</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2686,27 +2621,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>11:11</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall. På bilden syns det äldre ringhacket, men det färska som sitter strax ovanför syns desto sämre. Med kikare i fält syns det färska ringhacket betydligt bättre.</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2721,67 +2641,65 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136492698</t>
+          <t>https://artportalen.se/Sighting/137323297</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>136492701</v>
+        <v>137307954</v>
       </c>
       <c r="B20" t="n">
-        <v>58008</v>
+        <v>79537</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6434</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Slätberget, Ång</t>
+          <t>Fälleberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>647146</v>
+        <v>647884</v>
       </c>
       <c r="R20" t="n">
-        <v>6942952</v>
+        <v>6944388</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2808,27 +2726,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:15</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Färska och årsfärska ringhack på tall</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2837,76 +2750,87 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136492701</t>
+          <t>https://artportalen.se/Sighting/137307954</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>136492702</v>
+        <v>137320454</v>
       </c>
       <c r="B21" t="n">
-        <v>58008</v>
+        <v>5188</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>100526</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Slätberget, Ång</t>
+          <t>Frölandsberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>647143</v>
+        <v>647825</v>
       </c>
       <c r="R21" t="n">
-        <v>6942924</v>
+        <v>6944444</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2930,27 +2854,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>11:18</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>11:18</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2965,44 +2879,44 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136492702</t>
+          <t>https://artportalen.se/Sighting/137320454</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>136492704</v>
+        <v>137320885</v>
       </c>
       <c r="B22" t="n">
-        <v>58008</v>
+        <v>58189</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>103023</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3011,27 +2925,19 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Slätberget, Ång</t>
+          <t>Frölandsberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>647146</v>
+        <v>647865</v>
       </c>
       <c r="R22" t="n">
-        <v>6942908</v>
+        <v>6944435</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3055,27 +2961,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>11:25</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>11:25</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ca 2 meter ovan mark i asp. Hade inget måttband med mig varför bohålsdiametern inte kunde mätas. Hålet såg dock relativt litet ut varför jag bedömer det som sannolikt uthackat av tretåig hackspett.</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3090,74 +2981,65 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136492704</t>
+          <t>https://artportalen.se/Sighting/137320885</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>136492703</v>
+        <v>137320456</v>
       </c>
       <c r="B23" t="n">
-        <v>99372</v>
+        <v>5208</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Slätberget, Ång</t>
+          <t>Frölandsberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>647146</v>
+        <v>647824</v>
       </c>
       <c r="R23" t="n">
-        <v>6942908</v>
+        <v>6944445</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3181,22 +3063,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>11:21</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>11:21</t>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3211,71 +3088,62 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136492703</t>
+          <t>https://artportalen.se/Sighting/137320456</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1322962</v>
+        <v>137322935</v>
       </c>
       <c r="B24" t="n">
-        <v>93197</v>
+        <v>98270</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>221946</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Malarna N, Ång</t>
+          <t>Frölandsberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>647245</v>
+        <v>647565</v>
       </c>
       <c r="R24" t="n">
-        <v>6943405</v>
+        <v>6943957</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3302,12 +3170,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3318,45 +3186,31 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>Hällmarkstallskog</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr">
-        <is>
-          <t>Steget Före</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1322962</t>
+          <t>https://artportalen.se/Sighting/137322935</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1322963</v>
+        <v>136492696</v>
       </c>
       <c r="B25" t="n">
-        <v>93197</v>
+        <v>93426</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3381,29 +3235,20 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Malarna N, Ång</t>
+          <t>Slätberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>647228</v>
+        <v>647044</v>
       </c>
       <c r="R25" t="n">
-        <v>6943441</v>
+        <v>6943285</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3427,12 +3272,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3443,42 +3298,28 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>Hällmarkstallskog</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr">
-        <is>
-          <t>Steget Före</t>
-        </is>
-      </c>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1322963</t>
+          <t>https://artportalen.se/Sighting/136492696</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1763368</v>
+        <v>1763367</v>
       </c>
       <c r="B26" t="n">
         <v>93235</v>
@@ -3508,7 +3349,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3518,14 +3359,14 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Malarna N, Ång</t>
+          <t>Malarna, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>647245</v>
+        <v>647086</v>
       </c>
       <c r="R26" t="n">
-        <v>6943405</v>
+        <v>6943195</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3597,16 +3438,16 @@
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1763368</t>
+          <t>https://artportalen.se/Sighting/1763367</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1763369</v>
+        <v>136492698</v>
       </c>
       <c r="B27" t="n">
-        <v>93235</v>
+        <v>58008</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3614,46 +3455,45 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5966</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Malarna N, Ång</t>
+          <t>Slätberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>647228</v>
+        <v>647146</v>
       </c>
       <c r="R27" t="n">
-        <v>6943441</v>
+        <v>6942982</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3677,12 +3517,27 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall. På bilden syns det äldre ringhacket, men det färska som sitter strax ovanför syns desto sämre. Med kikare i fält syns det färska ringhacket betydligt bättre.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3693,45 +3548,31 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>Hällmarkstallskog</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr">
-        <is>
-          <t>Steget Före</t>
-        </is>
-      </c>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1763369</t>
+          <t>https://artportalen.se/Sighting/136492698</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>136492692</v>
+        <v>136492701</v>
       </c>
       <c r="B28" t="n">
-        <v>79517</v>
+        <v>58008</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3739,34 +3580,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Slätberget, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>646499</v>
+        <v>647146</v>
       </c>
       <c r="R28" t="n">
-        <v>6943041</v>
+        <v>6942952</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3798,7 +3644,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3808,7 +3654,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Färska och årsfärska ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3834,16 +3685,16 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136492692</t>
+          <t>https://artportalen.se/Sighting/136492701</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>136727074</v>
+        <v>136492702</v>
       </c>
       <c r="B29" t="n">
-        <v>79545</v>
+        <v>58008</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3851,38 +3702,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lomtjärnberget, Lomtjärnberget, Ång</t>
+          <t>Slätberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>646493</v>
+        <v>647143</v>
       </c>
       <c r="R29" t="n">
-        <v>6943045</v>
+        <v>6942924</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3906,22 +3761,27 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3936,27 +3796,27 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136727074</t>
+          <t>https://artportalen.se/Sighting/136492702</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>136729186</v>
+        <v>136492704</v>
       </c>
       <c r="B30" t="n">
-        <v>92429</v>
+        <v>58008</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3964,37 +3824,45 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lomtjärnen, Lomtjärnen, Ång</t>
+          <t>Slätberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>646697</v>
+        <v>647146</v>
       </c>
       <c r="R30" t="n">
-        <v>6943184</v>
+        <v>6942908</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4018,22 +3886,27 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ca 2 meter ovan mark i asp. Hade inget måttband med mig varför bohålsdiametern inte kunde mätas. Hålet såg dock relativt litet ut varför jag bedömer det som sannolikt uthackat av tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4048,65 +3921,74 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136729186</t>
+          <t>https://artportalen.se/Sighting/136492704</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>136729010</v>
+        <v>136492703</v>
       </c>
       <c r="B31" t="n">
-        <v>92158</v>
+        <v>99372</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lomtjärnen, Lomtjärnen, Ång</t>
+          <t>Slätberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>646709</v>
+        <v>647146</v>
       </c>
       <c r="R31" t="n">
-        <v>6943225</v>
+        <v>6942908</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4130,22 +4012,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4160,27 +4042,27 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136729010</t>
+          <t>https://artportalen.se/Sighting/136492703</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>136729373</v>
+        <v>1322962</v>
       </c>
       <c r="B32" t="n">
-        <v>92158</v>
+        <v>93197</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4188,34 +4070,43 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lomtjärnen, Lomtjärnen, Ång</t>
+          <t>Malarna N, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>646714</v>
+        <v>647245</v>
       </c>
       <c r="R32" t="n">
-        <v>6943267</v>
+        <v>6943405</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4242,22 +4133,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>14:21</t>
+          <t>2011-10-13</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>14:21</t>
+          <t>2011-10-13</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4268,31 +4149,45 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>Hällmarkstallskog</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Hans Sundström</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr"/>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Steget Före</t>
+        </is>
+      </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136729373</t>
+          <t>https://artportalen.se/Sighting/1322962</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>136730129</v>
+        <v>1322963</v>
       </c>
       <c r="B33" t="n">
-        <v>93447</v>
+        <v>93197</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4300,37 +4195,46 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lomtjärnen, Lomtjärnen, Ång</t>
+          <t>Malarna N, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>646794</v>
+        <v>647228</v>
       </c>
       <c r="R33" t="n">
-        <v>6943303</v>
+        <v>6943441</v>
       </c>
       <c r="S33" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4354,22 +4258,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>14:49</t>
+          <t>2011-10-13</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>14:49</t>
+          <t>2011-10-13</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4380,31 +4274,45 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>Hällmarkstallskog</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Hans Sundström</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr"/>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Steget Före</t>
+        </is>
+      </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136730129</t>
+          <t>https://artportalen.se/Sighting/1322963</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>1322965</v>
+        <v>1763368</v>
       </c>
       <c r="B34" t="n">
-        <v>93197</v>
+        <v>93235</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4412,26 +4320,26 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4445,10 +4353,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>647065</v>
+        <v>647245</v>
       </c>
       <c r="R34" t="n">
-        <v>6943550</v>
+        <v>6943405</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4520,16 +4428,16 @@
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1322965</t>
+          <t>https://artportalen.se/Sighting/1763368</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>1323582</v>
+        <v>1763369</v>
       </c>
       <c r="B35" t="n">
-        <v>93197</v>
+        <v>93235</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4537,26 +4445,26 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4566,14 +4474,14 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Lomtjärn S, Ång</t>
+          <t>Malarna N, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>646475</v>
+        <v>647228</v>
       </c>
       <c r="R35" t="n">
-        <v>6942960</v>
+        <v>6943441</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4600,12 +4508,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2011-10-24</t>
+          <t>2011-10-13</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2011-10-24</t>
+          <t>2011-10-13</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4645,16 +4553,16 @@
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1323582</t>
+          <t>https://artportalen.se/Sighting/1763369</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>136729947</v>
+        <v>136492692</v>
       </c>
       <c r="B36" t="n">
-        <v>93455</v>
+        <v>79517</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4662,37 +4570,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>185</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Lomtjärnen, Lomtjärnen, Ång</t>
+          <t>Slätberget, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>646748</v>
+        <v>646499</v>
       </c>
       <c r="R36" t="n">
-        <v>6943319</v>
+        <v>6943041</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4716,22 +4624,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4746,27 +4654,27 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136729947</t>
+          <t>https://artportalen.se/Sighting/136492692</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>136730396</v>
+        <v>136727074</v>
       </c>
       <c r="B37" t="n">
-        <v>93455</v>
+        <v>79545</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4774,37 +4682,38 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>185</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Bergmyrorna, Bergmyrorna, Ång</t>
+          <t>Lomtjärnberget, Lomtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>646858</v>
+        <v>646493</v>
       </c>
       <c r="R37" t="n">
-        <v>6943381</v>
+        <v>6943045</v>
       </c>
       <c r="S37" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4833,7 +4742,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4843,7 +4752,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4869,36 +4778,40 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136730396</t>
+          <t>https://artportalen.se/Sighting/136727074</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>136729099</v>
+        <v>136729186</v>
       </c>
       <c r="B38" t="n">
-        <v>92551</v>
+        <v>92430</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4877</v>
+        <v>658</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Leptoporus mollis/erubescens</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr"/>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4906,10 +4819,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>646693</v>
+        <v>646697</v>
       </c>
       <c r="R38" t="n">
-        <v>6943233</v>
+        <v>6943184</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -4941,7 +4854,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4951,7 +4864,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4977,16 +4890,16 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136729099</t>
+          <t>https://artportalen.se/Sighting/136729186</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>1568573</v>
+        <v>136729010</v>
       </c>
       <c r="B39" t="n">
-        <v>91930</v>
+        <v>92159</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4994,34 +4907,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Lomtjärnen S - Malarna, Ång</t>
+          <t>Lomtjärnen, Lomtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>646461</v>
+        <v>646709</v>
       </c>
       <c r="R39" t="n">
-        <v>6942878</v>
+        <v>6943225</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5048,12 +4961,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2012-11-19</t>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2012-11-19</t>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5064,50 +4987,31 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>hällmarkstallskog, nyckelbiotopsklass</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>på en grymt fin kort hällmarkstall, 200 - 300 årig</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr">
-        <is>
-          <t>Steget Före</t>
-        </is>
-      </c>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1568573</t>
+          <t>https://artportalen.se/Sighting/136729010</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>136730530</v>
+        <v>136729373</v>
       </c>
       <c r="B40" t="n">
-        <v>92179</v>
+        <v>92159</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5115,21 +5019,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5139,10 +5043,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>646758</v>
+        <v>646714</v>
       </c>
       <c r="R40" t="n">
-        <v>6943396</v>
+        <v>6943267</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5174,7 +5078,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5184,7 +5088,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5210,16 +5114,16 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136730530</t>
+          <t>https://artportalen.se/Sighting/136729373</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>136727898</v>
+        <v>136730129</v>
       </c>
       <c r="B41" t="n">
-        <v>93481</v>
+        <v>93448</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5227,37 +5131,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5448</v>
+        <v>4361</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lomtjärnberget, Lomtjärnberget, Ång</t>
+          <t>Lomtjärnen, Lomtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>646675</v>
+        <v>646794</v>
       </c>
       <c r="R41" t="n">
-        <v>6943107</v>
+        <v>6943303</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5286,7 +5190,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5296,7 +5200,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5311,27 +5215,27 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136727898</t>
+          <t>https://artportalen.se/Sighting/136730129</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>136730668</v>
+        <v>1322965</v>
       </c>
       <c r="B42" t="n">
-        <v>93481</v>
+        <v>93197</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5339,34 +5243,43 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5448</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lomtjärnen, Lomtjärnen, Ång</t>
+          <t>Malarna N, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>646756</v>
+        <v>647065</v>
       </c>
       <c r="R42" t="n">
-        <v>6943391</v>
+        <v>6943550</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5393,22 +5306,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>15:19</t>
+          <t>2011-10-13</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>15:19</t>
+          <t>2011-10-13</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5419,31 +5322,45 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>Hällmarkstallskog</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Hans Sundström</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
-        </is>
-      </c>
-      <c r="AY42" t="inlineStr"/>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>Steget Före</t>
+        </is>
+      </c>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136730668</t>
+          <t>https://artportalen.se/Sighting/1322965</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>1763371</v>
+        <v>1323582</v>
       </c>
       <c r="B43" t="n">
-        <v>93235</v>
+        <v>93197</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5451,26 +5368,26 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5480,14 +5397,14 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Malarna N, Ång</t>
+          <t>Lomtjärn S, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>647088</v>
+        <v>646475</v>
       </c>
       <c r="R43" t="n">
-        <v>6943543</v>
+        <v>6942960</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5514,12 +5431,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2011-10-24</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2011-10-24</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5559,16 +5476,16 @@
       </c>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1763371</t>
+          <t>https://artportalen.se/Sighting/1323582</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>1763372</v>
+        <v>136729947</v>
       </c>
       <c r="B44" t="n">
-        <v>93235</v>
+        <v>93456</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5576,43 +5493,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Malarna N, Ång</t>
+          <t>Lomtjärnen, Lomtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>647055</v>
+        <v>646748</v>
       </c>
       <c r="R44" t="n">
-        <v>6943589</v>
+        <v>6943319</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5639,12 +5547,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5659,31 +5577,27 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr">
-        <is>
-          <t>Steget Före</t>
-        </is>
-      </c>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1763372</t>
+          <t>https://artportalen.se/Sighting/136729947</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>136727620</v>
+        <v>136730396</v>
       </c>
       <c r="B45" t="n">
-        <v>93493</v>
+        <v>93456</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5691,37 +5605,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Lomtjärnberget, Lomtjärnberget, Ång</t>
+          <t>Bergmyrorna, Bergmyrorna, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>646650</v>
+        <v>646858</v>
       </c>
       <c r="R45" t="n">
-        <v>6943101</v>
+        <v>6943381</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5750,7 +5664,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5760,7 +5674,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5775,51 +5689,47 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136727620</t>
+          <t>https://artportalen.se/Sighting/136730396</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>136728890</v>
+        <v>136729099</v>
       </c>
       <c r="B46" t="n">
-        <v>93493</v>
+        <v>92552</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5966</v>
+        <v>4877</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
+          <t>Leptoporus mollis/erubescens</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5827,13 +5737,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>646729</v>
+        <v>646693</v>
       </c>
       <c r="R46" t="n">
-        <v>6943226</v>
+        <v>6943233</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5862,7 +5772,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5872,7 +5782,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5887,27 +5797,27 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136728890</t>
+          <t>https://artportalen.se/Sighting/136729099</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>136729950</v>
+        <v>1568573</v>
       </c>
       <c r="B47" t="n">
-        <v>93493</v>
+        <v>91930</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5915,37 +5825,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Lomtjärnen, Lomtjärnen, Ång</t>
+          <t>Lomtjärnen S - Malarna, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>646748</v>
+        <v>646461</v>
       </c>
       <c r="R47" t="n">
-        <v>6943318</v>
+        <v>6942878</v>
       </c>
       <c r="S47" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5969,22 +5879,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>14:43</t>
+          <t>2012-11-19</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>14:43</t>
+          <t>2012-11-19</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5995,31 +5895,50 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>hällmarkstallskog, nyckelbiotopsklass</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>på en grymt fin kort hällmarkstall, 200 - 300 årig</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Hans Sundström</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr"/>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>Steget Före</t>
+        </is>
+      </c>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136729950</t>
+          <t>https://artportalen.se/Sighting/1568573</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>136730208</v>
+        <v>136730530</v>
       </c>
       <c r="B48" t="n">
-        <v>93493</v>
+        <v>92180</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6027,21 +5946,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6051,13 +5970,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>646806</v>
+        <v>646758</v>
       </c>
       <c r="R48" t="n">
-        <v>6943312</v>
+        <v>6943396</v>
       </c>
       <c r="S48" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6086,7 +6005,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6096,7 +6015,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6111,27 +6030,27 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136730208</t>
+          <t>https://artportalen.se/Sighting/136730530</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>136730233</v>
+        <v>136727898</v>
       </c>
       <c r="B49" t="n">
-        <v>93493</v>
+        <v>93482</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6139,34 +6058,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5966</v>
+        <v>5448</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Bergmyrorna, Bergmyrorna, Ång</t>
+          <t>Lomtjärnberget, Lomtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>646832</v>
+        <v>646675</v>
       </c>
       <c r="R49" t="n">
-        <v>6943339</v>
+        <v>6943107</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6198,7 +6117,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6208,7 +6127,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6234,16 +6153,16 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136730233</t>
+          <t>https://artportalen.se/Sighting/136727898</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>136730274</v>
+        <v>136730668</v>
       </c>
       <c r="B50" t="n">
-        <v>93493</v>
+        <v>93482</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6251,34 +6170,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5966</v>
+        <v>5448</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Bergmyrorna, Bergmyrorna, Ång</t>
+          <t>Lomtjärnen, Lomtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>646842</v>
+        <v>646756</v>
       </c>
       <c r="R50" t="n">
-        <v>6943352</v>
+        <v>6943391</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6310,7 +6229,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6320,7 +6239,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6346,16 +6265,16 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136730274</t>
+          <t>https://artportalen.se/Sighting/136730668</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>136730463</v>
+        <v>1763371</v>
       </c>
       <c r="B51" t="n">
-        <v>93493</v>
+        <v>93235</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6380,20 +6299,29 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Bergmyrorna, Bergmyrorna, Ång</t>
+          <t>Malarna N, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>646862</v>
+        <v>647088</v>
       </c>
       <c r="R51" t="n">
-        <v>6943380</v>
+        <v>6943543</v>
       </c>
       <c r="S51" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6417,22 +6345,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>15:04</t>
+          <t>2011-10-13</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>15:04</t>
+          <t>2011-10-13</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6443,69 +6361,92 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>Hällmarkstallskog</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Hans Sundström</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
-        </is>
-      </c>
-      <c r="AY51" t="inlineStr"/>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>Steget Före</t>
+        </is>
+      </c>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136730463</t>
+          <t>https://artportalen.se/Sighting/1763371</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>136492693</v>
+        <v>1763372</v>
       </c>
       <c r="B52" t="n">
-        <v>79509</v>
+        <v>93235</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6434</v>
+        <v>5966</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Slätberget, Ång</t>
+          <t>Malarna N, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>646690</v>
+        <v>647055</v>
       </c>
       <c r="R52" t="n">
-        <v>6943229</v>
+        <v>6943589</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6529,22 +6470,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>10:27</t>
+          <t>2011-10-13</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>10:27</t>
+          <t>2011-10-13</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6559,66 +6490,69 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Hans Sundström</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
-        </is>
-      </c>
-      <c r="AY52" t="inlineStr"/>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>Steget Före</t>
+        </is>
+      </c>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136492693</t>
+          <t>https://artportalen.se/Sighting/1763372</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>136728918</v>
+        <v>136727620</v>
       </c>
       <c r="B53" t="n">
-        <v>58030</v>
+        <v>93494</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Lomtjärnen, Lomtjärnen, Ång</t>
+          <t>Lomtjärnberget, Lomtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>646676</v>
+        <v>646650</v>
       </c>
       <c r="R53" t="n">
-        <v>6943222</v>
+        <v>6943101</v>
       </c>
       <c r="S53" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6647,7 +6581,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6657,7 +6591,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6672,66 +6606,65 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136728918</t>
+          <t>https://artportalen.se/Sighting/136727620</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>136730508</v>
+        <v>136728890</v>
       </c>
       <c r="B54" t="n">
-        <v>58030</v>
+        <v>93494</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Bergmyrorna, Bergmyrorna, Ång</t>
+          <t>Lomtjärnen, Lomtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>646851</v>
+        <v>646729</v>
       </c>
       <c r="R54" t="n">
-        <v>6943419</v>
+        <v>6943226</v>
       </c>
       <c r="S54" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6760,7 +6693,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6770,7 +6703,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6785,27 +6718,27 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136730508</t>
+          <t>https://artportalen.se/Sighting/136728890</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>136492695</v>
+        <v>136729950</v>
       </c>
       <c r="B55" t="n">
-        <v>58008</v>
+        <v>93494</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6813,51 +6746,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>5966</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Slätberget, Ång</t>
+          <t>Lomtjärnen, Lomtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>646997</v>
+        <v>646748</v>
       </c>
       <c r="R55" t="n">
-        <v>6943476</v>
+        <v>6943318</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6881,22 +6800,22 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6911,27 +6830,27 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136492695</t>
+          <t>https://artportalen.se/Sighting/136729950</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>136728716</v>
+        <v>136730208</v>
       </c>
       <c r="B56" t="n">
-        <v>58033</v>
+        <v>93494</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6939,35 +6858,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>5966</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Lomtjärnen, Lomtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>646643</v>
+        <v>646806</v>
       </c>
       <c r="R56" t="n">
-        <v>6943205</v>
+        <v>6943312</v>
       </c>
       <c r="S56" t="n">
         <v>20</v>
@@ -6999,7 +6917,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7009,12 +6927,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:46</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7040,51 +6953,51 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136728716</t>
+          <t>https://artportalen.se/Sighting/136730208</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>136729240</v>
+        <v>136730233</v>
       </c>
       <c r="B57" t="n">
-        <v>5188</v>
+        <v>93494</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100526</v>
+        <v>5966</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Lomtjärnen, Lomtjärnen, Ång</t>
+          <t>Bergmyrorna, Bergmyrorna, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>646709</v>
+        <v>646832</v>
       </c>
       <c r="R57" t="n">
-        <v>6943259</v>
+        <v>6943339</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7116,7 +7029,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7126,7 +7039,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7152,16 +7065,16 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136729240</t>
+          <t>https://artportalen.se/Sighting/136730233</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>136492694</v>
+        <v>136730274</v>
       </c>
       <c r="B58" t="n">
-        <v>92520</v>
+        <v>93494</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7169,37 +7082,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6040186</v>
+        <v>5966</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Slätberget, Ång</t>
+          <t>Bergmyrorna, Bergmyrorna, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>646699</v>
+        <v>646842</v>
       </c>
       <c r="R58" t="n">
-        <v>6943225</v>
+        <v>6943352</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7223,22 +7136,22 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7247,23 +7160,941 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136730274</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>136730463</v>
+      </c>
+      <c r="B59" t="n">
+        <v>93494</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Bergmyrorna, Bergmyrorna, Ång</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>646862</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6943380</v>
+      </c>
+      <c r="S59" t="n">
+        <v>20</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136730463</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>136492693</v>
+      </c>
+      <c r="B60" t="n">
+        <v>79509</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Slätberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>646690</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6943229</v>
+      </c>
+      <c r="S60" t="n">
+        <v>5</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136492693</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>136728918</v>
+      </c>
+      <c r="B61" t="n">
+        <v>58030</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Lomtjärnen, Lomtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>646676</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6943222</v>
+      </c>
+      <c r="S61" t="n">
+        <v>20</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136728918</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>136730508</v>
+      </c>
+      <c r="B62" t="n">
+        <v>58030</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Bergmyrorna, Bergmyrorna, Ång</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>646851</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6943419</v>
+      </c>
+      <c r="S62" t="n">
+        <v>20</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136730508</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>136492695</v>
+      </c>
+      <c r="B63" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Slätberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>646997</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6943476</v>
+      </c>
+      <c r="S63" t="n">
+        <v>5</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136492695</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>136728716</v>
+      </c>
+      <c r="B64" t="n">
+        <v>58033</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Lomtjärnen, Lomtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>646643</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6943205</v>
+      </c>
+      <c r="S64" t="n">
+        <v>20</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136728716</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>136729240</v>
+      </c>
+      <c r="B65" t="n">
+        <v>5188</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Lomtjärnen, Lomtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>646709</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6943259</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136729240</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>136492694</v>
+      </c>
+      <c r="B66" t="n">
+        <v>92520</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Slätberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>646699</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6943225</v>
+      </c>
+      <c r="S66" t="n">
+        <v>5</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF66" t="inlineStr"/>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136492694</t>
         </is>
@@ -7328,6 +8159,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 47711-2024 artfynd.xlsx
+++ b/artfynd/A 47711-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ66"/>
+  <dimension ref="A1:AZ67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6047,10 +6047,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>136727898</v>
+        <v>137354803</v>
       </c>
       <c r="B49" t="n">
-        <v>93482</v>
+        <v>92180</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6058,37 +6058,44 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5448</v>
+        <v>5442</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Lomtjärnberget, Lomtjärnberget, Ång</t>
+          <t>Lomtjärn, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>646675</v>
+        <v>646766</v>
       </c>
       <c r="R49" t="n">
-        <v>6943107</v>
+        <v>6943207</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6112,22 +6119,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6136,30 +6143,31 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Jonatan Fözö</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Jonatan Fözö</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136727898</t>
+          <t>https://artportalen.se/Sighting/137354803</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>136730668</v>
+        <v>136727898</v>
       </c>
       <c r="B50" t="n">
         <v>93482</v>
@@ -6190,14 +6198,14 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Lomtjärnen, Lomtjärnen, Ång</t>
+          <t>Lomtjärnberget, Lomtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>646756</v>
+        <v>646675</v>
       </c>
       <c r="R50" t="n">
-        <v>6943391</v>
+        <v>6943107</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6229,7 +6237,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6239,7 +6247,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6265,16 +6273,16 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136730668</t>
+          <t>https://artportalen.se/Sighting/136727898</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>1763371</v>
+        <v>136730668</v>
       </c>
       <c r="B51" t="n">
-        <v>93235</v>
+        <v>93482</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6282,43 +6290,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5966</v>
+        <v>5448</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Malarna N, Ång</t>
+          <t>Lomtjärnen, Lomtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>647088</v>
+        <v>646756</v>
       </c>
       <c r="R51" t="n">
-        <v>6943543</v>
+        <v>6943391</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6345,12 +6344,22 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2011-10-13</t>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6361,42 +6370,28 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AI51" t="inlineStr">
-        <is>
-          <t>Hällmarkstallskog</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
-        </is>
-      </c>
-      <c r="AY51" t="inlineStr">
-        <is>
-          <t>Steget Före</t>
-        </is>
-      </c>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1763371</t>
+          <t>https://artportalen.se/Sighting/136730668</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>1763372</v>
+        <v>1763371</v>
       </c>
       <c r="B52" t="n">
         <v>93235</v>
@@ -6426,7 +6421,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -6440,10 +6435,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>647055</v>
+        <v>647088</v>
       </c>
       <c r="R52" t="n">
-        <v>6943589</v>
+        <v>6943543</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6487,6 +6482,16 @@
       <c r="AG52" t="b">
         <v>0</v>
       </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>Hällmarkstallskog</t>
+        </is>
+      </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
@@ -6505,16 +6510,16 @@
       </c>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1763372</t>
+          <t>https://artportalen.se/Sighting/1763371</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>136727620</v>
+        <v>1763372</v>
       </c>
       <c r="B53" t="n">
-        <v>93494</v>
+        <v>93235</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6539,17 +6544,26 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Lomtjärnberget, Lomtjärnberget, Ång</t>
+          <t>Malarna N, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>646650</v>
+        <v>647055</v>
       </c>
       <c r="R53" t="n">
-        <v>6943101</v>
+        <v>6943589</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6576,22 +6590,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>12:55</t>
+          <t>2011-10-13</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>12:55</t>
+          <t>2011-10-13</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6606,24 +6610,28 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Hans Sundström</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
-        </is>
-      </c>
-      <c r="AY53" t="inlineStr"/>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>Steget Före</t>
+        </is>
+      </c>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136727620</t>
+          <t>https://artportalen.se/Sighting/1763372</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>136728890</v>
+        <v>136727620</v>
       </c>
       <c r="B54" t="n">
         <v>93494</v>
@@ -6654,14 +6662,14 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Lomtjärnen, Lomtjärnen, Ång</t>
+          <t>Lomtjärnberget, Lomtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>646729</v>
+        <v>646650</v>
       </c>
       <c r="R54" t="n">
-        <v>6943226</v>
+        <v>6943101</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6693,7 +6701,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6703,7 +6711,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6729,13 +6737,13 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136728890</t>
+          <t>https://artportalen.se/Sighting/136727620</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>136729950</v>
+        <v>136728890</v>
       </c>
       <c r="B55" t="n">
         <v>93494</v>
@@ -6770,13 +6778,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>646748</v>
+        <v>646729</v>
       </c>
       <c r="R55" t="n">
-        <v>6943318</v>
+        <v>6943226</v>
       </c>
       <c r="S55" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6805,7 +6813,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6815,7 +6823,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6830,24 +6838,24 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136729950</t>
+          <t>https://artportalen.se/Sighting/136728890</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>136730208</v>
+        <v>136729950</v>
       </c>
       <c r="B56" t="n">
         <v>93494</v>
@@ -6882,10 +6890,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>646806</v>
+        <v>646748</v>
       </c>
       <c r="R56" t="n">
-        <v>6943312</v>
+        <v>6943318</v>
       </c>
       <c r="S56" t="n">
         <v>20</v>
@@ -6917,7 +6925,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6927,7 +6935,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6953,13 +6961,13 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136730208</t>
+          <t>https://artportalen.se/Sighting/136729950</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>136730233</v>
+        <v>136730208</v>
       </c>
       <c r="B57" t="n">
         <v>93494</v>
@@ -6990,17 +6998,17 @@
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Bergmyrorna, Bergmyrorna, Ång</t>
+          <t>Lomtjärnen, Lomtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>646832</v>
+        <v>646806</v>
       </c>
       <c r="R57" t="n">
-        <v>6943339</v>
+        <v>6943312</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7029,7 +7037,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7039,7 +7047,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7054,24 +7062,24 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136730233</t>
+          <t>https://artportalen.se/Sighting/136730208</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>136730274</v>
+        <v>136730233</v>
       </c>
       <c r="B58" t="n">
         <v>93494</v>
@@ -7106,10 +7114,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>646842</v>
+        <v>646832</v>
       </c>
       <c r="R58" t="n">
-        <v>6943352</v>
+        <v>6943339</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7141,7 +7149,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7151,7 +7159,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7177,13 +7185,13 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136730274</t>
+          <t>https://artportalen.se/Sighting/136730233</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>136730463</v>
+        <v>136730274</v>
       </c>
       <c r="B59" t="n">
         <v>93494</v>
@@ -7218,13 +7226,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>646862</v>
+        <v>646842</v>
       </c>
       <c r="R59" t="n">
-        <v>6943380</v>
+        <v>6943352</v>
       </c>
       <c r="S59" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7253,7 +7261,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7263,7 +7271,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7278,65 +7286,65 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136730463</t>
+          <t>https://artportalen.se/Sighting/136730274</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>136492693</v>
+        <v>136730463</v>
       </c>
       <c r="B60" t="n">
-        <v>79509</v>
+        <v>93494</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6434</v>
+        <v>5966</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Slätberget, Ång</t>
+          <t>Bergmyrorna, Bergmyrorna, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>646690</v>
+        <v>646862</v>
       </c>
       <c r="R60" t="n">
-        <v>6943229</v>
+        <v>6943380</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7360,22 +7368,22 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7390,27 +7398,27 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136492693</t>
+          <t>https://artportalen.se/Sighting/136730463</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>136728918</v>
+        <v>136492693</v>
       </c>
       <c r="B61" t="n">
-        <v>58030</v>
+        <v>79509</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7418,38 +7426,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100049</v>
+        <v>6434</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Lomtjärnen, Lomtjärnen, Ång</t>
+          <t>Slätberget, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>646676</v>
+        <v>646690</v>
       </c>
       <c r="R61" t="n">
-        <v>6943222</v>
+        <v>6943229</v>
       </c>
       <c r="S61" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7473,22 +7480,22 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7503,24 +7510,24 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136728918</t>
+          <t>https://artportalen.se/Sighting/136492693</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>136730508</v>
+        <v>136728918</v>
       </c>
       <c r="B62" t="n">
         <v>58030</v>
@@ -7552,14 +7559,14 @@
       <c r="M62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Bergmyrorna, Bergmyrorna, Ång</t>
+          <t>Lomtjärnen, Lomtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>646851</v>
+        <v>646676</v>
       </c>
       <c r="R62" t="n">
-        <v>6943419</v>
+        <v>6943222</v>
       </c>
       <c r="S62" t="n">
         <v>20</v>
@@ -7591,7 +7598,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7601,7 +7608,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7627,33 +7634,33 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136730508</t>
+          <t>https://artportalen.se/Sighting/136728918</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>136492695</v>
+        <v>136730508</v>
       </c>
       <c r="B63" t="n">
-        <v>58008</v>
+        <v>58030</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -7661,34 +7668,21 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Slätberget, Ång</t>
+          <t>Bergmyrorna, Bergmyrorna, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>646997</v>
+        <v>646851</v>
       </c>
       <c r="R63" t="n">
-        <v>6943476</v>
+        <v>6943419</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7712,22 +7706,22 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7742,27 +7736,27 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136492695</t>
+          <t>https://artportalen.se/Sighting/136730508</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>136728716</v>
+        <v>136492695</v>
       </c>
       <c r="B64" t="n">
-        <v>58033</v>
+        <v>58008</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7787,21 +7781,34 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Lomtjärnen, Lomtjärnen, Ång</t>
+          <t>Slätberget, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>646643</v>
+        <v>646997</v>
       </c>
       <c r="R64" t="n">
-        <v>6943205</v>
+        <v>6943476</v>
       </c>
       <c r="S64" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7825,27 +7832,22 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>13:46</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7860,65 +7862,66 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136728716</t>
+          <t>https://artportalen.se/Sighting/136492695</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>136729240</v>
+        <v>136728716</v>
       </c>
       <c r="B65" t="n">
-        <v>5188</v>
+        <v>58033</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Lomtjärnen, Lomtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>646709</v>
+        <v>646643</v>
       </c>
       <c r="R65" t="n">
-        <v>6943259</v>
+        <v>6943205</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7947,7 +7950,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7957,7 +7960,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7972,65 +7980,65 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136729240</t>
+          <t>https://artportalen.se/Sighting/136728716</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>136492694</v>
+        <v>136729240</v>
       </c>
       <c r="B66" t="n">
-        <v>92520</v>
+        <v>5188</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6040186</v>
+        <v>100526</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Slätberget, Ång</t>
+          <t>Lomtjärnen, Lomtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>646699</v>
+        <v>646709</v>
       </c>
       <c r="R66" t="n">
-        <v>6943225</v>
+        <v>6943259</v>
       </c>
       <c r="S66" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8054,22 +8062,22 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8078,23 +8086,135 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136729240</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>136492694</v>
+      </c>
+      <c r="B67" t="n">
+        <v>92520</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Slätberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>646699</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6943225</v>
+      </c>
+      <c r="S67" t="n">
+        <v>5</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Säbrå</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF67" t="inlineStr"/>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136492694</t>
         </is>
@@ -8167,6 +8287,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 47711-2024 artfynd.xlsx
+++ b/artfynd/A 47711-2024 artfynd.xlsx
@@ -1019,7 +1019,7 @@
         <v>137306841</v>
       </c>
       <c r="B5" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>137307957</v>
       </c>
       <c r="B6" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>137306302</v>
       </c>
       <c r="B7" t="n">
-        <v>79580</v>
+        <v>79583</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>137306578</v>
       </c>
       <c r="B8" t="n">
-        <v>79580</v>
+        <v>79583</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>137325198</v>
       </c>
       <c r="B9" t="n">
-        <v>79580</v>
+        <v>79583</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>137326956</v>
       </c>
       <c r="B10" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v>137303806</v>
       </c>
       <c r="B11" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>137304584</v>
       </c>
       <c r="B12" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>137326463</v>
       </c>
       <c r="B13" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         <v>137303303</v>
       </c>
       <c r="B15" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
         <v>137323297</v>
       </c>
       <c r="B19" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>137307954</v>
       </c>
       <c r="B20" t="n">
-        <v>79537</v>
+        <v>79540</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
         <v>137320885</v>
       </c>
       <c r="B22" t="n">
-        <v>58189</v>
+        <v>58190</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>137322935</v>
       </c>
       <c r="B24" t="n">
-        <v>98270</v>
+        <v>98275</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -6050,7 +6050,7 @@
         <v>137354803</v>
       </c>
       <c r="B49" t="n">
-        <v>92180</v>
+        <v>92183</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 47711-2024 artfynd.xlsx
+++ b/artfynd/A 47711-2024 artfynd.xlsx
@@ -1019,7 +1019,7 @@
         <v>137306841</v>
       </c>
       <c r="B5" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>137307957</v>
       </c>
       <c r="B6" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>137326956</v>
       </c>
       <c r="B10" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v>137303806</v>
       </c>
       <c r="B11" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>137304584</v>
       </c>
       <c r="B12" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         <v>137303303</v>
       </c>
       <c r="B15" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
         <v>137323297</v>
       </c>
       <c r="B19" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>137322935</v>
       </c>
       <c r="B24" t="n">
-        <v>98275</v>
+        <v>98277</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -6050,7 +6050,7 @@
         <v>137354803</v>
       </c>
       <c r="B49" t="n">
-        <v>92183</v>
+        <v>92185</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 47711-2024 artfynd.xlsx
+++ b/artfynd/A 47711-2024 artfynd.xlsx
@@ -1019,7 +1019,7 @@
         <v>137306841</v>
       </c>
       <c r="B5" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>137307957</v>
       </c>
       <c r="B6" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>137306302</v>
       </c>
       <c r="B7" t="n">
-        <v>79583</v>
+        <v>79588</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>137306578</v>
       </c>
       <c r="B8" t="n">
-        <v>79583</v>
+        <v>79588</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>137325198</v>
       </c>
       <c r="B9" t="n">
-        <v>79583</v>
+        <v>79588</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>137326956</v>
       </c>
       <c r="B10" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v>137303806</v>
       </c>
       <c r="B11" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>137304584</v>
       </c>
       <c r="B12" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>137326463</v>
       </c>
       <c r="B13" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         <v>137303303</v>
       </c>
       <c r="B15" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
         <v>137323297</v>
       </c>
       <c r="B19" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>137307954</v>
       </c>
       <c r="B20" t="n">
-        <v>79540</v>
+        <v>79545</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
         <v>137320885</v>
       </c>
       <c r="B22" t="n">
-        <v>58190</v>
+        <v>58191</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>137322935</v>
       </c>
       <c r="B24" t="n">
-        <v>98277</v>
+        <v>98283</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -6050,7 +6050,7 @@
         <v>137354803</v>
       </c>
       <c r="B49" t="n">
-        <v>92185</v>
+        <v>92190</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 47711-2024 artfynd.xlsx
+++ b/artfynd/A 47711-2024 artfynd.xlsx
@@ -1019,7 +1019,7 @@
         <v>137306841</v>
       </c>
       <c r="B5" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>137307957</v>
       </c>
       <c r="B6" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>137306302</v>
       </c>
       <c r="B7" t="n">
-        <v>79588</v>
+        <v>79599</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>137306578</v>
       </c>
       <c r="B8" t="n">
-        <v>79588</v>
+        <v>79599</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>137325198</v>
       </c>
       <c r="B9" t="n">
-        <v>79588</v>
+        <v>79599</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>137326956</v>
       </c>
       <c r="B10" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v>137303806</v>
       </c>
       <c r="B11" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>137304584</v>
       </c>
       <c r="B12" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>137326463</v>
       </c>
       <c r="B13" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         <v>137303303</v>
       </c>
       <c r="B15" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
         <v>137323297</v>
       </c>
       <c r="B19" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>137307954</v>
       </c>
       <c r="B20" t="n">
-        <v>79545</v>
+        <v>79556</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>137322935</v>
       </c>
       <c r="B24" t="n">
-        <v>98283</v>
+        <v>98295</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -6050,7 +6050,7 @@
         <v>137354803</v>
       </c>
       <c r="B49" t="n">
-        <v>92190</v>
+        <v>92202</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 47711-2024 artfynd.xlsx
+++ b/artfynd/A 47711-2024 artfynd.xlsx
@@ -1019,7 +1019,7 @@
         <v>137306841</v>
       </c>
       <c r="B5" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>137307957</v>
       </c>
       <c r="B6" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>137306302</v>
       </c>
       <c r="B7" t="n">
-        <v>79599</v>
+        <v>79600</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>137306578</v>
       </c>
       <c r="B8" t="n">
-        <v>79599</v>
+        <v>79600</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>137325198</v>
       </c>
       <c r="B9" t="n">
-        <v>79599</v>
+        <v>79600</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>137326956</v>
       </c>
       <c r="B10" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v>137303806</v>
       </c>
       <c r="B11" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>137304584</v>
       </c>
       <c r="B12" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>137326463</v>
       </c>
       <c r="B13" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         <v>137303303</v>
       </c>
       <c r="B15" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
         <v>137323297</v>
       </c>
       <c r="B19" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>137307954</v>
       </c>
       <c r="B20" t="n">
-        <v>79556</v>
+        <v>79557</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>137322935</v>
       </c>
       <c r="B24" t="n">
-        <v>98295</v>
+        <v>98296</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -6050,7 +6050,7 @@
         <v>137354803</v>
       </c>
       <c r="B49" t="n">
-        <v>92202</v>
+        <v>92203</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 47711-2024 artfynd.xlsx
+++ b/artfynd/A 47711-2024 artfynd.xlsx
@@ -1019,7 +1019,7 @@
         <v>137306841</v>
       </c>
       <c r="B5" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>137307957</v>
       </c>
       <c r="B6" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>137306302</v>
       </c>
       <c r="B7" t="n">
-        <v>79600</v>
+        <v>79602</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>137306578</v>
       </c>
       <c r="B8" t="n">
-        <v>79600</v>
+        <v>79602</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>137325198</v>
       </c>
       <c r="B9" t="n">
-        <v>79600</v>
+        <v>79602</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>137326956</v>
       </c>
       <c r="B10" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v>137303806</v>
       </c>
       <c r="B11" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>137304584</v>
       </c>
       <c r="B12" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>137326463</v>
       </c>
       <c r="B13" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         <v>137303303</v>
       </c>
       <c r="B15" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
         <v>137323297</v>
       </c>
       <c r="B19" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>137307954</v>
       </c>
       <c r="B20" t="n">
-        <v>79557</v>
+        <v>79559</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>137322935</v>
       </c>
       <c r="B24" t="n">
-        <v>98296</v>
+        <v>98299</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -6050,7 +6050,7 @@
         <v>137354803</v>
       </c>
       <c r="B49" t="n">
-        <v>92203</v>
+        <v>92206</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 47711-2024 artfynd.xlsx
+++ b/artfynd/A 47711-2024 artfynd.xlsx
@@ -1019,7 +1019,7 @@
         <v>137306841</v>
       </c>
       <c r="B5" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>137307957</v>
       </c>
       <c r="B6" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>137306302</v>
       </c>
       <c r="B7" t="n">
-        <v>79602</v>
+        <v>79606</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>137306578</v>
       </c>
       <c r="B8" t="n">
-        <v>79602</v>
+        <v>79606</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>137325198</v>
       </c>
       <c r="B9" t="n">
-        <v>79602</v>
+        <v>79606</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>137326956</v>
       </c>
       <c r="B10" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v>137303806</v>
       </c>
       <c r="B11" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>137304584</v>
       </c>
       <c r="B12" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>137326463</v>
       </c>
       <c r="B13" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         <v>137303303</v>
       </c>
       <c r="B15" t="n">
-        <v>92148</v>
+        <v>92152</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
         <v>137323297</v>
       </c>
       <c r="B19" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>137307954</v>
       </c>
       <c r="B20" t="n">
-        <v>79559</v>
+        <v>79563</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
         <v>137320885</v>
       </c>
       <c r="B22" t="n">
-        <v>58191</v>
+        <v>58194</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>137322935</v>
       </c>
       <c r="B24" t="n">
-        <v>98299</v>
+        <v>98303</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -6050,7 +6050,7 @@
         <v>137354803</v>
       </c>
       <c r="B49" t="n">
-        <v>92206</v>
+        <v>92210</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
